--- a/automatizacion/empaquetados.xlsx
+++ b/automatizacion/empaquetados.xlsx
@@ -1,27 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Empaquetados" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Listas" sheetId="3" state="hidden" r:id="rId3"/>
+    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Empaquetados" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Listas" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Empaquetados'!$A$5:$AD$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Empaquetados'!$A$5:$AD$106</definedName>
   </definedNames>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -37,25 +36,25 @@
     <font>
       <name val="Arial"/>
       <i val="1"/>
-      <color rgb="00595959"/>
+      <color rgb="FF595959"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="001F1F1F"/>
+      <color rgb="FF1F1F1F"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="001F4E78"/>
+      <color rgb="FF1F4E78"/>
       <sz val="8"/>
     </font>
     <font>
@@ -71,8 +70,13 @@
       <b val="1"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="14">
     <fill>
       <patternFill/>
     </fill>
@@ -81,37 +85,62 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
+        <fgColor rgb="FF1F4E78"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00BDD7EE"/>
+        <fgColor rgb="FFBDD7EE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
+        <fgColor rgb="FFE2EFDA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00808080"/>
+        <fgColor rgb="FF808080"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF375623"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEDEDED"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EDEDED"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D08E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00DDEBF7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00375623"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00EDEDED"/>
       </patternFill>
     </fill>
   </fills>
@@ -125,23 +154,24 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </left>
       <right style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </right>
       <top style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </top>
       <bottom style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -194,9 +224,25 @@
     <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -560,12 +606,12 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:A20"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" outlineLevelCol="0"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="17.4" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Registro de tarifas empaquetadas (BORRADOR)</t>
@@ -580,7 +626,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr"/>
+      <c r="A3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -618,7 +664,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr"/>
+      <c r="A9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -677,7 +723,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr"/>
+      <c r="A18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -705,7 +751,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:AD1005"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" outlineLevelCol="0"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
@@ -713,8 +759,7 @@
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="7" max="8"/>
     <col width="11" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="10" max="10"/>
     <col width="13" customWidth="1" min="11" max="11"/>
@@ -739,7 +784,7 @@
     <col width="40" customWidth="1" min="30" max="30"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="17.4" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Tarifas empaquetadas</t>
@@ -982,7 +1027,7 @@
       </c>
       <c r="C6" s="17" t="inlineStr">
         <is>
-          <t>TE-EMP-CM-001</t>
+          <t>TE-EMP-CM-101</t>
         </is>
       </c>
       <c r="D6" s="18" t="inlineStr">
@@ -1000,57 +1045,77 @@
           <t>Residencial</t>
         </is>
       </c>
-      <c r="G6" s="19" t="inlineStr"/>
-      <c r="H6" s="19" t="inlineStr"/>
-      <c r="I6" s="19" t="inlineStr"/>
+      <c r="G6" s="19" t="n"/>
+      <c r="H6" s="19" t="n"/>
+      <c r="I6" s="19" t="n">
+        <v>10</v>
+      </c>
       <c r="J6" s="19" t="inlineStr">
         <is>
           <t>https://www.prueba.com</t>
         </is>
       </c>
-      <c r="K6" s="19" t="inlineStr">
-        <is>
-          <t>014567890</t>
-        </is>
+      <c r="K6" s="19" t="n">
+        <v>14856321</v>
       </c>
       <c r="L6" s="19" t="inlineStr">
         <is>
-          <t>atencion@prueba.pe</t>
+          <t>prueba@gmail.com</t>
         </is>
       </c>
       <c r="M6" s="19" t="inlineStr">
         <is>
-          <t>Dúo fijo + móvil</t>
+          <t>4 servicios: TF + TVP + IF + SMP</t>
         </is>
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>TE-TFP-CM-001</t>
-        </is>
-      </c>
-      <c r="O6" s="19" t="inlineStr"/>
+          <t>TE-TF-CM-001</t>
+        </is>
+      </c>
+      <c r="O6" s="19" t="n"/>
       <c r="P6" s="19" t="inlineStr">
         <is>
+          <t>TE-TVP-CM-001</t>
+        </is>
+      </c>
+      <c r="Q6" s="19" t="n"/>
+      <c r="R6" s="19" t="inlineStr">
+        <is>
+          <t>TE-IF-CM-003</t>
+        </is>
+      </c>
+      <c r="S6" s="19" t="n"/>
+      <c r="T6" s="19" t="inlineStr">
+        <is>
           <t>TE-SMP-CM-001</t>
         </is>
       </c>
-      <c r="Q6" s="19" t="inlineStr"/>
-      <c r="R6" s="19" t="inlineStr"/>
-      <c r="S6" s="19" t="inlineStr"/>
-      <c r="T6" s="19" t="inlineStr"/>
-      <c r="U6" s="19" t="inlineStr"/>
-      <c r="V6" s="19" t="inlineStr"/>
-      <c r="W6" s="19" t="inlineStr"/>
-      <c r="X6" s="19" t="inlineStr"/>
-      <c r="Y6" s="19" t="inlineStr"/>
+      <c r="U6" s="19" t="n"/>
+      <c r="V6" s="19" t="n"/>
+      <c r="W6" s="19" t="n"/>
+      <c r="X6" s="19" t="n"/>
+      <c r="Y6" s="19" t="n"/>
       <c r="Z6" s="20">
         <f>IF(C6="","",COUNTA(N6,P6,R6,T6,V6,X6))</f>
         <v/>
       </c>
-      <c r="AA6" s="21" t="inlineStr"/>
+      <c r="AA6" s="24" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
       <c r="AB6" s="21" t="inlineStr"/>
-      <c r="AC6" s="21" t="inlineStr"/>
-      <c r="AD6" s="21" t="inlineStr"/>
+      <c r="AC6" s="21" t="inlineStr">
+        <is>
+          <t>2026-10-20 10:10:17</t>
+        </is>
+      </c>
+      <c r="AD6" s="21" t="inlineStr">
+        <is>
+          <t>paquete confirmado | registro definitivo OK (disponibilidad: Lima)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="16" t="n">
@@ -1063,7 +1128,7 @@
       </c>
       <c r="C7" s="17" t="inlineStr">
         <is>
-          <t>TE-EMP-CM-002</t>
+          <t>TE-EMP-CM-102</t>
         </is>
       </c>
       <c r="D7" s="18" t="inlineStr">
@@ -1081,61 +1146,77 @@
           <t>Residencial</t>
         </is>
       </c>
-      <c r="G7" s="19" t="inlineStr"/>
-      <c r="H7" s="19" t="inlineStr"/>
-      <c r="I7" s="19" t="inlineStr"/>
+      <c r="G7" s="19" t="n"/>
+      <c r="H7" s="19" t="n"/>
+      <c r="I7" s="19" t="n">
+        <v>10</v>
+      </c>
       <c r="J7" s="19" t="inlineStr">
         <is>
           <t>https://www.prueba.com</t>
         </is>
       </c>
-      <c r="K7" s="19" t="inlineStr">
-        <is>
-          <t>014567890</t>
-        </is>
+      <c r="K7" s="19" t="n">
+        <v>14856321</v>
       </c>
       <c r="L7" s="19" t="inlineStr">
         <is>
-          <t>atencion@prueba.pe</t>
+          <t>prueba@gmail.com</t>
         </is>
       </c>
       <c r="M7" s="19" t="inlineStr">
         <is>
-          <t>Trío fijo + internet + TV</t>
+          <t>4 servicios: TF + TVP + IF + SMC</t>
         </is>
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>TE-TF-CM-001</t>
-        </is>
-      </c>
-      <c r="O7" s="19" t="inlineStr"/>
+          <t>TE-TF-CM-004</t>
+        </is>
+      </c>
+      <c r="O7" s="19" t="n"/>
       <c r="P7" s="19" t="inlineStr">
         <is>
-          <t>TE-IF-CM-003</t>
-        </is>
-      </c>
-      <c r="Q7" s="19" t="inlineStr"/>
+          <t>TE-TVP-CM-004</t>
+        </is>
+      </c>
+      <c r="Q7" s="19" t="n"/>
       <c r="R7" s="19" t="inlineStr">
         <is>
-          <t>TE-TVP-CM-001</t>
-        </is>
-      </c>
-      <c r="S7" s="19" t="inlineStr"/>
-      <c r="T7" s="19" t="inlineStr"/>
-      <c r="U7" s="19" t="inlineStr"/>
-      <c r="V7" s="19" t="inlineStr"/>
-      <c r="W7" s="19" t="inlineStr"/>
-      <c r="X7" s="19" t="inlineStr"/>
-      <c r="Y7" s="19" t="inlineStr"/>
+          <t>TE-IF-CM-005</t>
+        </is>
+      </c>
+      <c r="S7" s="19" t="n"/>
+      <c r="T7" s="19" t="inlineStr">
+        <is>
+          <t>TE-SMC-CM-001</t>
+        </is>
+      </c>
+      <c r="U7" s="19" t="n"/>
+      <c r="V7" s="19" t="n"/>
+      <c r="W7" s="19" t="n"/>
+      <c r="X7" s="19" t="n"/>
+      <c r="Y7" s="19" t="n"/>
       <c r="Z7" s="20">
         <f>IF(C7="","",COUNTA(N7,P7,R7,T7,V7,X7))</f>
         <v/>
       </c>
-      <c r="AA7" s="21" t="inlineStr"/>
+      <c r="AA7" s="24" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
       <c r="AB7" s="21" t="inlineStr"/>
-      <c r="AC7" s="21" t="inlineStr"/>
-      <c r="AD7" s="21" t="inlineStr"/>
+      <c r="AC7" s="21" t="inlineStr">
+        <is>
+          <t>2026-10-20 10:58:47</t>
+        </is>
+      </c>
+      <c r="AD7" s="21" t="inlineStr">
+        <is>
+          <t>paquete confirmado | registro definitivo OK (disponibilidad: Lima)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="16" t="n">
@@ -1148,7 +1229,7 @@
       </c>
       <c r="C8" s="17" t="inlineStr">
         <is>
-          <t>TE-EMP-CM-003</t>
+          <t>TE-EMP-CM-103</t>
         </is>
       </c>
       <c r="D8" s="18" t="inlineStr">
@@ -1166,65 +1247,77 @@
           <t>Residencial</t>
         </is>
       </c>
-      <c r="G8" s="19" t="inlineStr"/>
-      <c r="H8" s="19" t="inlineStr"/>
-      <c r="I8" s="19" t="inlineStr"/>
+      <c r="G8" s="19" t="n"/>
+      <c r="H8" s="19" t="n"/>
+      <c r="I8" s="19" t="n">
+        <v>10</v>
+      </c>
       <c r="J8" s="19" t="inlineStr">
         <is>
           <t>https://www.prueba.com</t>
         </is>
       </c>
-      <c r="K8" s="19" t="inlineStr">
-        <is>
-          <t>014567890</t>
-        </is>
+      <c r="K8" s="19" t="n">
+        <v>14856321</v>
       </c>
       <c r="L8" s="19" t="inlineStr">
         <is>
-          <t>atencion@prueba.pe</t>
+          <t>prueba@gmail.com</t>
         </is>
       </c>
       <c r="M8" s="19" t="inlineStr">
         <is>
-          <t>Valores escritos a mano</t>
+          <t>4 servicios: TF + TVP + IF + SMO</t>
         </is>
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>TE-SMC-CM-001</t>
-        </is>
-      </c>
-      <c r="O8" s="19" t="inlineStr">
-        <is>
-          <t>18.9</t>
-        </is>
-      </c>
+          <t>TE-TF-CM-007</t>
+        </is>
+      </c>
+      <c r="O8" s="19" t="n"/>
       <c r="P8" s="19" t="inlineStr">
         <is>
-          <t>TE-OS-CM-001</t>
-        </is>
-      </c>
-      <c r="Q8" s="19" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="R8" s="19" t="inlineStr"/>
-      <c r="S8" s="19" t="inlineStr"/>
-      <c r="T8" s="19" t="inlineStr"/>
-      <c r="U8" s="19" t="inlineStr"/>
-      <c r="V8" s="19" t="inlineStr"/>
-      <c r="W8" s="19" t="inlineStr"/>
-      <c r="X8" s="19" t="inlineStr"/>
-      <c r="Y8" s="19" t="inlineStr"/>
+          <t>TE-TVP-CM-007</t>
+        </is>
+      </c>
+      <c r="Q8" s="19" t="n"/>
+      <c r="R8" s="19" t="inlineStr">
+        <is>
+          <t>TE-IF-CM-009</t>
+        </is>
+      </c>
+      <c r="S8" s="19" t="n"/>
+      <c r="T8" s="19" t="inlineStr">
+        <is>
+          <t>TE-SMO-CM-001</t>
+        </is>
+      </c>
+      <c r="U8" s="19" t="n"/>
+      <c r="V8" s="19" t="n"/>
+      <c r="W8" s="19" t="n"/>
+      <c r="X8" s="19" t="n"/>
+      <c r="Y8" s="19" t="n"/>
       <c r="Z8" s="20">
         <f>IF(C8="","",COUNTA(N8,P8,R8,T8,V8,X8))</f>
         <v/>
       </c>
-      <c r="AA8" s="21" t="inlineStr"/>
+      <c r="AA8" s="24" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
       <c r="AB8" s="21" t="inlineStr"/>
-      <c r="AC8" s="21" t="inlineStr"/>
-      <c r="AD8" s="21" t="inlineStr"/>
+      <c r="AC8" s="21" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:01:04</t>
+        </is>
+      </c>
+      <c r="AD8" s="21" t="inlineStr">
+        <is>
+          <t>paquete confirmado | registro definitivo OK (disponibilidad: Lima)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="16" t="n">
@@ -1237,7 +1330,7 @@
       </c>
       <c r="C9" s="17" t="inlineStr">
         <is>
-          <t>TE-EMP-CM-004</t>
+          <t>TE-EMP-CM-104</t>
         </is>
       </c>
       <c r="D9" s="18" t="inlineStr">
@@ -1252,70 +1345,82 @@
       </c>
       <c r="F9" s="19" t="inlineStr">
         <is>
-          <t>Comercial</t>
-        </is>
-      </c>
-      <c r="G9" s="19" t="inlineStr"/>
-      <c r="H9" s="19" t="inlineStr"/>
-      <c r="I9" s="19" t="inlineStr"/>
+          <t>Residencial</t>
+        </is>
+      </c>
+      <c r="G9" s="19" t="n"/>
+      <c r="H9" s="19" t="n"/>
+      <c r="I9" s="19" t="n">
+        <v>10</v>
+      </c>
       <c r="J9" s="19" t="inlineStr">
         <is>
           <t>https://www.prueba.com</t>
         </is>
       </c>
-      <c r="K9" s="19" t="inlineStr">
-        <is>
-          <t>014567890</t>
-        </is>
+      <c r="K9" s="19" t="n">
+        <v>14856321</v>
       </c>
       <c r="L9" s="19" t="inlineStr">
         <is>
-          <t>atencion@prueba.pe</t>
+          <t>prueba@gmail.com</t>
         </is>
       </c>
       <c r="M9" s="19" t="inlineStr">
         <is>
-          <t>Cuatro servicios, alcance comercial</t>
+          <t>4 servicios: TF + TVP + IF + SMQ</t>
         </is>
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>TE-TFP-CM-002</t>
-        </is>
-      </c>
-      <c r="O9" s="19" t="inlineStr"/>
+          <t>TE-TF-CM-001</t>
+        </is>
+      </c>
+      <c r="O9" s="19" t="n"/>
       <c r="P9" s="19" t="inlineStr">
         <is>
-          <t>TE-TVP-CM-002</t>
-        </is>
-      </c>
-      <c r="Q9" s="19" t="inlineStr"/>
+          <t>TE-TVP-CM-010</t>
+        </is>
+      </c>
+      <c r="Q9" s="19" t="n"/>
       <c r="R9" s="19" t="inlineStr">
         <is>
-          <t>TE-SMP-CM-004</t>
-        </is>
-      </c>
-      <c r="S9" s="19" t="inlineStr"/>
+          <t>TE-IF-CM-003</t>
+        </is>
+      </c>
+      <c r="S9" s="19" t="n"/>
       <c r="T9" s="19" t="inlineStr">
         <is>
-          <t>TE-AC-CM-004</t>
-        </is>
-      </c>
-      <c r="U9" s="19" t="inlineStr"/>
-      <c r="V9" s="19" t="inlineStr"/>
-      <c r="W9" s="19" t="inlineStr"/>
-      <c r="X9" s="19" t="inlineStr"/>
-      <c r="Y9" s="19" t="inlineStr"/>
+          <t>TE-SMQ-CM-001</t>
+        </is>
+      </c>
+      <c r="U9" s="19" t="n"/>
+      <c r="V9" s="19" t="n"/>
+      <c r="W9" s="19" t="n"/>
+      <c r="X9" s="19" t="n"/>
+      <c r="Y9" s="19" t="n"/>
       <c r="Z9" s="20">
         <f>IF(C9="","",COUNTA(N9,P9,R9,T9,V9,X9))</f>
         <v/>
       </c>
-      <c r="AA9" s="21" t="inlineStr"/>
+      <c r="AA9" s="24" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
       <c r="AB9" s="21" t="inlineStr"/>
-      <c r="AC9" s="21" t="inlineStr"/>
-      <c r="AD9" s="21" t="inlineStr"/>
-    </row>
-    <row r="10">
+      <c r="AC9" s="21" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:01:25</t>
+        </is>
+      </c>
+      <c r="AD9" s="21" t="inlineStr">
+        <is>
+          <t>paquete confirmado | registro definitivo OK (disponibilidad: Lima)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22.8" customHeight="1">
       <c r="A10" s="16" t="n">
         <v>5</v>
       </c>
@@ -1326,7 +1431,7 @@
       </c>
       <c r="C10" s="17" t="inlineStr">
         <is>
-          <t>TE-EMP-CM-005</t>
+          <t>TE-EMP-CM-105</t>
         </is>
       </c>
       <c r="D10" s="18" t="inlineStr">
@@ -1341,635 +1446,8799 @@
       </c>
       <c r="F10" s="19" t="inlineStr">
         <is>
-          <t>Residencial + Comercial</t>
-        </is>
-      </c>
-      <c r="G10" s="19" t="inlineStr"/>
-      <c r="H10" s="19" t="inlineStr"/>
-      <c r="I10" s="19" t="inlineStr"/>
+          <t>Residencial</t>
+        </is>
+      </c>
+      <c r="G10" s="19" t="n"/>
+      <c r="H10" s="19" t="n"/>
+      <c r="I10" s="19" t="n">
+        <v>10</v>
+      </c>
       <c r="J10" s="19" t="inlineStr">
         <is>
           <t>https://www.prueba.com</t>
         </is>
       </c>
-      <c r="K10" s="19" t="inlineStr">
-        <is>
-          <t>014567890</t>
-        </is>
+      <c r="K10" s="19" t="n">
+        <v>14856321</v>
       </c>
       <c r="L10" s="19" t="inlineStr">
         <is>
-          <t>atencion@prueba.pe</t>
+          <t>prueba@gmail.com</t>
         </is>
       </c>
       <c r="M10" s="19" t="inlineStr">
         <is>
-          <t>Alcance doble</t>
+          <t>4 servicios: TF + TVP + PIF + SMP</t>
         </is>
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>TE-TF-CM-003</t>
-        </is>
-      </c>
-      <c r="O10" s="19" t="inlineStr"/>
+          <t>TE-TF-CM-004</t>
+        </is>
+      </c>
+      <c r="O10" s="19" t="n"/>
       <c r="P10" s="19" t="inlineStr">
         <is>
-          <t>TE-TVP-CM-003</t>
-        </is>
-      </c>
-      <c r="Q10" s="19" t="inlineStr"/>
-      <c r="R10" s="19" t="inlineStr"/>
-      <c r="S10" s="19" t="inlineStr"/>
-      <c r="T10" s="19" t="inlineStr"/>
-      <c r="U10" s="19" t="inlineStr"/>
-      <c r="V10" s="19" t="inlineStr"/>
-      <c r="W10" s="19" t="inlineStr"/>
-      <c r="X10" s="19" t="inlineStr"/>
-      <c r="Y10" s="19" t="inlineStr"/>
+          <t>TE-TVP-CM-001</t>
+        </is>
+      </c>
+      <c r="Q10" s="19" t="n"/>
+      <c r="R10" s="19" t="inlineStr">
+        <is>
+          <t>TE-PIF-CM-003</t>
+        </is>
+      </c>
+      <c r="S10" s="19" t="n"/>
+      <c r="T10" s="19" t="inlineStr">
+        <is>
+          <t>TE-SMP-CM-002</t>
+        </is>
+      </c>
+      <c r="U10" s="19" t="n"/>
+      <c r="V10" s="19" t="n"/>
+      <c r="W10" s="19" t="n"/>
+      <c r="X10" s="19" t="n"/>
+      <c r="Y10" s="19" t="n"/>
       <c r="Z10" s="20">
         <f>IF(C10="","",COUNTA(N10,P10,R10,T10,V10,X10))</f>
         <v/>
       </c>
-      <c r="AA10" s="21" t="inlineStr"/>
+      <c r="AA10" s="24" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
       <c r="AB10" s="21" t="inlineStr"/>
-      <c r="AC10" s="21" t="inlineStr"/>
-      <c r="AD10" s="21" t="inlineStr"/>
+      <c r="AC10" s="21" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:01:45</t>
+        </is>
+      </c>
+      <c r="AD10" s="21" t="inlineStr">
+        <is>
+          <t>paquete confirmado | registro definitivo OK (disponibilidad: Lima)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>TE-EMP-CM-106</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Residencial</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>10</v>
+      </c>
+      <c r="J11" s="19" t="inlineStr">
+        <is>
+          <t>https://www.prueba.com</t>
+        </is>
+      </c>
+      <c r="K11" s="19" t="n">
+        <v>14856321</v>
+      </c>
+      <c r="L11" s="19" t="inlineStr">
+        <is>
+          <t>prueba@gmail.com</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>4 servicios: TF + TVP + PIF + SMC</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>TE-TF-CM-007</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>TE-TVP-CM-004</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>TE-PIF-CM-005</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>TE-SMC-CM-002</t>
+        </is>
+      </c>
       <c r="Z11" s="20">
         <f>IF(C11="","",COUNTA(N11,P11,R11,T11,V11,X11))</f>
         <v/>
       </c>
+      <c r="AA11" s="28" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:59:35</t>
+        </is>
+      </c>
+      <c r="AD11" s="2" t="inlineStr">
+        <is>
+          <t>Ya figura como registrado en el lote EXCEL (no se repitió). | registro definitivo OK (disponibilidad: Lima)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>TE-EMP-CM-107</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Residencial</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>10</v>
+      </c>
+      <c r="J12" s="19" t="inlineStr">
+        <is>
+          <t>https://www.prueba.com</t>
+        </is>
+      </c>
+      <c r="K12" s="19" t="n">
+        <v>14856321</v>
+      </c>
+      <c r="L12" s="19" t="inlineStr">
+        <is>
+          <t>prueba@gmail.com</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>4 servicios: TF + TVP + PIF + SMO</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>TE-TF-CM-001</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>TE-TVP-CM-007</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>TE-PIF-CM-009</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>TE-SMO-CM-002</t>
+        </is>
+      </c>
       <c r="Z12" s="20">
         <f>IF(C12="","",COUNTA(N12,P12,R12,T12,V12,X12))</f>
         <v/>
       </c>
+      <c r="AA12" s="28" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:07:41</t>
+        </is>
+      </c>
+      <c r="AD12" s="2" t="inlineStr">
+        <is>
+          <t>paquete confirmado | registro definitivo OK (disponibilidad: Lima)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>TE-EMP-CM-108</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Residencial</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>10</v>
+      </c>
+      <c r="J13" s="19" t="inlineStr">
+        <is>
+          <t>https://www.prueba.com</t>
+        </is>
+      </c>
+      <c r="K13" s="19" t="n">
+        <v>14856321</v>
+      </c>
+      <c r="L13" s="19" t="inlineStr">
+        <is>
+          <t>prueba@gmail.com</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>4 servicios: TF + TVP + PIF + SMQ</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>TE-TF-CM-004</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>TE-TVP-CM-010</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>TE-PIF-CM-003</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>TE-SMQ-CM-002</t>
+        </is>
+      </c>
       <c r="Z13" s="20">
         <f>IF(C13="","",COUNTA(N13,P13,R13,T13,V13,X13))</f>
         <v/>
       </c>
+      <c r="AA13" s="28" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:08:01</t>
+        </is>
+      </c>
+      <c r="AD13" s="2" t="inlineStr">
+        <is>
+          <t>paquete confirmado | registro definitivo OK (disponibilidad: Lima)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>TE-EMP-CM-109</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Residencial</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>10</v>
+      </c>
+      <c r="J14" s="19" t="inlineStr">
+        <is>
+          <t>https://www.prueba.com</t>
+        </is>
+      </c>
+      <c r="K14" s="19" t="n">
+        <v>14856321</v>
+      </c>
+      <c r="L14" s="19" t="inlineStr">
+        <is>
+          <t>prueba@gmail.com</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>4 servicios: TF + TVPR + IF + SMP</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>TE-TF-CM-007</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>TE-TVPR-CM-001</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>TE-IF-CM-005</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>TE-SMP-CM-003</t>
+        </is>
+      </c>
       <c r="Z14" s="20">
         <f>IF(C14="","",COUNTA(N14,P14,R14,T14,V14,X14))</f>
         <v/>
       </c>
+      <c r="AA14" s="28" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:08:22</t>
+        </is>
+      </c>
+      <c r="AD14" s="2" t="inlineStr">
+        <is>
+          <t>paquete confirmado | registro definitivo OK (disponibilidad: Lima)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>TE-EMP-CM-110</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Residencial</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>10</v>
+      </c>
+      <c r="J15" s="19" t="inlineStr">
+        <is>
+          <t>https://www.prueba.com</t>
+        </is>
+      </c>
+      <c r="K15" s="19" t="n">
+        <v>14856321</v>
+      </c>
+      <c r="L15" s="19" t="inlineStr">
+        <is>
+          <t>prueba@gmail.com</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>4 servicios: TF + TVPR + IF + SMC</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>TE-TF-CM-001</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>TE-TVPR-CM-004</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>TE-IF-CM-009</t>
+        </is>
+      </c>
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>TE-SMC-CM-003</t>
+        </is>
+      </c>
       <c r="Z15" s="20">
         <f>IF(C15="","",COUNTA(N15,P15,R15,T15,V15,X15))</f>
         <v/>
       </c>
+      <c r="AA15" s="28" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 12:00:01</t>
+        </is>
+      </c>
+      <c r="AD15" s="2" t="inlineStr">
+        <is>
+          <t>Ya figura como registrado en el lote EXCEL (no se repitió). | registro definitivo OK (disponibilidad: Lima)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>TE-EMP-CM-111</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Residencial</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>10</v>
+      </c>
+      <c r="J16" s="19" t="inlineStr">
+        <is>
+          <t>https://www.prueba.com</t>
+        </is>
+      </c>
+      <c r="K16" s="19" t="n">
+        <v>14856321</v>
+      </c>
+      <c r="L16" s="19" t="inlineStr">
+        <is>
+          <t>prueba@gmail.com</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>4 servicios: TF + TVPR + IF + SMO</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>TE-TF-CM-004</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>TE-TVPR-CM-007</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>TE-IF-CM-003</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>TE-SMO-CM-003</t>
+        </is>
+      </c>
       <c r="Z16" s="20">
         <f>IF(C16="","",COUNTA(N16,P16,R16,T16,V16,X16))</f>
         <v/>
       </c>
+      <c r="AA16" s="28" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:34:30</t>
+        </is>
+      </c>
+      <c r="AD16" s="2" t="inlineStr">
+        <is>
+          <t>paquete confirmado | registro definitivo OK (disponibilidad: Lima)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>TE-EMP-CM-112</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Residencial</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>10</v>
+      </c>
+      <c r="J17" s="19" t="inlineStr">
+        <is>
+          <t>https://www.prueba.com</t>
+        </is>
+      </c>
+      <c r="K17" s="19" t="n">
+        <v>14856321</v>
+      </c>
+      <c r="L17" s="19" t="inlineStr">
+        <is>
+          <t>prueba@gmail.com</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>4 servicios: TF + TVPR + IF + SMQ</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>TE-TF-CM-007</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>TE-TVPR-CM-010</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>TE-IF-CM-005</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>TE-SMQ-CM-003</t>
+        </is>
+      </c>
       <c r="Z17" s="20">
         <f>IF(C17="","",COUNTA(N17,P17,R17,T17,V17,X17))</f>
         <v/>
       </c>
+      <c r="AA17" s="28" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:34:52</t>
+        </is>
+      </c>
+      <c r="AD17" s="2" t="inlineStr">
+        <is>
+          <t>paquete confirmado | registro definitivo OK (disponibilidad: Lima)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>TE-EMP-CM-113</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Residencial</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>10</v>
+      </c>
+      <c r="J18" s="19" t="inlineStr">
+        <is>
+          <t>https://www.prueba.com</t>
+        </is>
+      </c>
+      <c r="K18" s="19" t="n">
+        <v>14856321</v>
+      </c>
+      <c r="L18" s="19" t="inlineStr">
+        <is>
+          <t>prueba@gmail.com</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>4 servicios: TF + TVPR + PIF + SMP</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>TE-TF-CM-001</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>TE-TVPR-CM-001</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>TE-PIF-CM-005</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>TE-SMP-CM-001</t>
+        </is>
+      </c>
       <c r="Z18" s="20">
         <f>IF(C18="","",COUNTA(N18,P18,R18,T18,V18,X18))</f>
         <v/>
       </c>
+      <c r="AA18" s="28" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:35:13</t>
+        </is>
+      </c>
+      <c r="AD18" s="2" t="inlineStr">
+        <is>
+          <t>paquete confirmado | registro definitivo OK (disponibilidad: Lima)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>TE-EMP-CM-114</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Residencial</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>10</v>
+      </c>
+      <c r="J19" s="19" t="inlineStr">
+        <is>
+          <t>https://www.prueba.com</t>
+        </is>
+      </c>
+      <c r="K19" s="19" t="n">
+        <v>14856321</v>
+      </c>
+      <c r="L19" s="19" t="inlineStr">
+        <is>
+          <t>prueba@gmail.com</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>4 servicios: TF + TVPR + PIF + SMC</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>TE-TF-CM-004</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>TE-TVPR-CM-004</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>TE-PIF-CM-009</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>TE-SMC-CM-001</t>
+        </is>
+      </c>
       <c r="Z19" s="20">
         <f>IF(C19="","",COUNTA(N19,P19,R19,T19,V19,X19))</f>
         <v/>
       </c>
+      <c r="AA19" s="28" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:35:34</t>
+        </is>
+      </c>
+      <c r="AD19" s="2" t="inlineStr">
+        <is>
+          <t>paquete confirmado | registro definitivo OK (disponibilidad: Lima)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>TE-EMP-CM-115</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Residencial</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>10</v>
+      </c>
+      <c r="J20" s="19" t="inlineStr">
+        <is>
+          <t>https://www.prueba.com</t>
+        </is>
+      </c>
+      <c r="K20" s="19" t="n">
+        <v>14856321</v>
+      </c>
+      <c r="L20" s="19" t="inlineStr">
+        <is>
+          <t>prueba@gmail.com</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>4 servicios: TF + TVPR + PIF + SMO</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>TE-TF-CM-007</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>TE-TVPR-CM-007</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>TE-PIF-CM-003</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>TE-SMO-CM-001</t>
+        </is>
+      </c>
       <c r="Z20" s="20">
         <f>IF(C20="","",COUNTA(N20,P20,R20,T20,V20,X20))</f>
         <v/>
       </c>
+      <c r="AA20" s="28" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:35:55</t>
+        </is>
+      </c>
+      <c r="AD20" s="2" t="inlineStr">
+        <is>
+          <t>paquete confirmado | registro definitivo OK (disponibilidad: Lima)</t>
+        </is>
+      </c>
     </row>
     <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>TE-EMP-CM-116</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Residencial</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>10</v>
+      </c>
+      <c r="J21" s="19" t="inlineStr">
+        <is>
+          <t>https://www.prueba.com</t>
+        </is>
+      </c>
+      <c r="K21" s="19" t="n">
+        <v>14856321</v>
+      </c>
+      <c r="L21" s="19" t="inlineStr">
+        <is>
+          <t>prueba@gmail.com</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>4 servicios: TF + TVPR + PIF + SMQ</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>TE-TF-CM-001</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>TE-TVPR-CM-010</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>TE-PIF-CM-005</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>TE-SMQ-CM-001</t>
+        </is>
+      </c>
       <c r="Z21" s="20">
         <f>IF(C21="","",COUNTA(N21,P21,R21,T21,V21,X21))</f>
         <v/>
       </c>
+      <c r="AA21" s="28" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:36:16</t>
+        </is>
+      </c>
+      <c r="AD21" s="2" t="inlineStr">
+        <is>
+          <t>paquete confirmado | registro definitivo OK (disponibilidad: Lima)</t>
+        </is>
+      </c>
     </row>
     <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>TE-EMP-CM-117</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Residencial</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>10</v>
+      </c>
+      <c r="J22" s="19" t="inlineStr">
+        <is>
+          <t>https://www.prueba.com</t>
+        </is>
+      </c>
+      <c r="K22" s="19" t="n">
+        <v>14856321</v>
+      </c>
+      <c r="L22" s="19" t="inlineStr">
+        <is>
+          <t>prueba@gmail.com</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>4 servicios: TF + PTV + IF + SMP</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>TE-TF-CM-004</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>TE-PTV-CM-001</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>TE-IF-CM-009</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>TE-SMP-CM-002</t>
+        </is>
+      </c>
       <c r="Z22" s="20">
         <f>IF(C22="","",COUNTA(N22,P22,R22,T22,V22,X22))</f>
         <v/>
       </c>
+      <c r="AA22" s="28" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:36:37</t>
+        </is>
+      </c>
+      <c r="AD22" s="2" t="inlineStr">
+        <is>
+          <t>paquete confirmado | registro definitivo OK (disponibilidad: Lima)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>TE-EMP-CM-118</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Residencial</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>10</v>
+      </c>
+      <c r="J23" s="19" t="inlineStr">
+        <is>
+          <t>https://www.prueba.com</t>
+        </is>
+      </c>
+      <c r="K23" s="19" t="n">
+        <v>14856321</v>
+      </c>
+      <c r="L23" s="19" t="inlineStr">
+        <is>
+          <t>prueba@gmail.com</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>4 servicios: TF + PTV + IF + SMC</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>TE-TF-CM-007</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>TE-PTV-CM-004</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>TE-IF-CM-003</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>TE-SMC-CM-002</t>
+        </is>
+      </c>
       <c r="Z23" s="20">
         <f>IF(C23="","",COUNTA(N23,P23,R23,T23,V23,X23))</f>
         <v/>
       </c>
+      <c r="AA23" s="28" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:37:00</t>
+        </is>
+      </c>
+      <c r="AD23" s="2" t="inlineStr">
+        <is>
+          <t>paquete confirmado | registro definitivo OK (disponibilidad: Lima)</t>
+        </is>
+      </c>
     </row>
     <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>TE-EMP-CM-119</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Residencial</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>10</v>
+      </c>
+      <c r="J24" s="19" t="inlineStr">
+        <is>
+          <t>https://www.prueba.com</t>
+        </is>
+      </c>
+      <c r="K24" s="19" t="n">
+        <v>14856321</v>
+      </c>
+      <c r="L24" s="19" t="inlineStr">
+        <is>
+          <t>prueba@gmail.com</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>4 servicios: TF + PTV + IF + SMO</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>TE-TF-CM-001</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>TE-PTV-CM-007</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>TE-IF-CM-005</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>TE-SMO-CM-002</t>
+        </is>
+      </c>
       <c r="Z24" s="20">
         <f>IF(C24="","",COUNTA(N24,P24,R24,T24,V24,X24))</f>
         <v/>
       </c>
+      <c r="AA24" s="28" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:37:22</t>
+        </is>
+      </c>
+      <c r="AD24" s="2" t="inlineStr">
+        <is>
+          <t>paquete confirmado | registro definitivo OK (disponibilidad: Lima)</t>
+        </is>
+      </c>
     </row>
     <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>TE-EMP-CM-120</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Residencial</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>10</v>
+      </c>
+      <c r="J25" s="19" t="inlineStr">
+        <is>
+          <t>https://www.prueba.com</t>
+        </is>
+      </c>
+      <c r="K25" s="19" t="n">
+        <v>14856321</v>
+      </c>
+      <c r="L25" s="19" t="inlineStr">
+        <is>
+          <t>prueba@gmail.com</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>4 servicios: TF + PTV + IF + SMQ</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>TE-TF-CM-004</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>TE-PTV-CM-010</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>TE-IF-CM-009</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>TE-SMQ-CM-002</t>
+        </is>
+      </c>
       <c r="Z25" s="20">
         <f>IF(C25="","",COUNTA(N25,P25,R25,T25,V25,X25))</f>
         <v/>
       </c>
+      <c r="AA25" s="28" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr"/>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:37:43</t>
+        </is>
+      </c>
+      <c r="AD25" s="2" t="inlineStr">
+        <is>
+          <t>paquete confirmado | registro definitivo OK (disponibilidad: Lima)</t>
+        </is>
+      </c>
     </row>
     <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>TE-EMP-CM-121</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Residencial</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>10</v>
+      </c>
+      <c r="J26" s="19" t="inlineStr">
+        <is>
+          <t>https://www.prueba.com</t>
+        </is>
+      </c>
+      <c r="K26" s="19" t="n">
+        <v>14856321</v>
+      </c>
+      <c r="L26" s="19" t="inlineStr">
+        <is>
+          <t>prueba@gmail.com</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>4 servicios: TF + PTV + PIF + SMP</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>TE-TF-CM-007</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>TE-PTV-CM-001</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>TE-PIF-CM-009</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>TE-SMP-CM-003</t>
+        </is>
+      </c>
       <c r="Z26" s="20">
         <f>IF(C26="","",COUNTA(N26,P26,R26,T26,V26,X26))</f>
         <v/>
       </c>
+      <c r="AA26" s="28" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr"/>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:38:04</t>
+        </is>
+      </c>
+      <c r="AD26" s="2" t="inlineStr">
+        <is>
+          <t>paquete confirmado | registro definitivo OK (disponibilidad: Lima)</t>
+        </is>
+      </c>
     </row>
     <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>TE-EMP-CM-122</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>Residencial</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>10</v>
+      </c>
+      <c r="J27" s="19" t="inlineStr">
+        <is>
+          <t>https://www.prueba.com</t>
+        </is>
+      </c>
+      <c r="K27" s="19" t="n">
+        <v>14856321</v>
+      </c>
+      <c r="L27" s="19" t="inlineStr">
+        <is>
+          <t>prueba@gmail.com</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>4 servicios: TF + PTV + PIF + SMC</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>TE-TF-CM-001</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>TE-PTV-CM-004</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t>TE-PIF-CM-003</t>
+        </is>
+      </c>
+      <c r="T27" s="2" t="inlineStr">
+        <is>
+          <t>TE-SMC-CM-003</t>
+        </is>
+      </c>
       <c r="Z27" s="20">
         <f>IF(C27="","",COUNTA(N27,P27,R27,T27,V27,X27))</f>
         <v/>
       </c>
+      <c r="AA27" s="28" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr"/>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:38:26</t>
+        </is>
+      </c>
+      <c r="AD27" s="2" t="inlineStr">
+        <is>
+          <t>paquete confirmado | registro definitivo OK (disponibilidad: Lima)</t>
+        </is>
+      </c>
     </row>
     <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>TE-EMP-CM-123</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Residencial</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>10</v>
+      </c>
+      <c r="J28" s="19" t="inlineStr">
+        <is>
+          <t>https://www.prueba.com</t>
+        </is>
+      </c>
+      <c r="K28" s="19" t="n">
+        <v>14856321</v>
+      </c>
+      <c r="L28" s="19" t="inlineStr">
+        <is>
+          <t>prueba@gmail.com</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>4 servicios: TF + PTV + PIF + SMO</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>TE-TF-CM-004</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>TE-PTV-CM-007</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>TE-PIF-CM-005</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>TE-SMO-CM-003</t>
+        </is>
+      </c>
       <c r="Z28" s="20">
         <f>IF(C28="","",COUNTA(N28,P28,R28,T28,V28,X28))</f>
         <v/>
       </c>
+      <c r="AA28" s="28" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr"/>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:38:47</t>
+        </is>
+      </c>
+      <c r="AD28" s="2" t="inlineStr">
+        <is>
+          <t>paquete confirmado | registro definitivo OK (disponibilidad: Lima)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>TE-EMP-CM-124</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>Residencial</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>10</v>
+      </c>
+      <c r="J29" s="19" t="inlineStr">
+        <is>
+          <t>https://www.prueba.com</t>
+        </is>
+      </c>
+      <c r="K29" s="19" t="n">
+        <v>14856321</v>
+      </c>
+      <c r="L29" s="19" t="inlineStr">
+        <is>
+          <t>prueba@gmail.com</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>4 servicios: TF + PTV + PIF + SMQ</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>TE-TF-CM-007</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>TE-PTV-CM-010</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>TE-PIF-CM-009</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>TE-SMQ-CM-003</t>
+        </is>
+      </c>
       <c r="Z29" s="20">
         <f>IF(C29="","",COUNTA(N29,P29,R29,T29,V29,X29))</f>
         <v/>
       </c>
+      <c r="AA29" s="28" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr"/>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:39:08</t>
+        </is>
+      </c>
+      <c r="AD29" s="2" t="inlineStr">
+        <is>
+          <t>paquete confirmado | registro definitivo OK (disponibilidad: Lima)</t>
+        </is>
+      </c>
     </row>
     <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>TE-EMP-CM-125</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>Residencial</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>10</v>
+      </c>
+      <c r="J30" s="19" t="inlineStr">
+        <is>
+          <t>https://www.prueba.com</t>
+        </is>
+      </c>
+      <c r="K30" s="19" t="n">
+        <v>14856321</v>
+      </c>
+      <c r="L30" s="19" t="inlineStr">
+        <is>
+          <t>prueba@gmail.com</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>4 servicios: TFP + TVP + IF + SMP</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>TE-TFP-CM-001</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>TE-TVP-CM-001</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>TE-IF-CM-003</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>TE-SMP-CM-001</t>
+        </is>
+      </c>
       <c r="Z30" s="20">
         <f>IF(C30="","",COUNTA(N30,P30,R30,T30,V30,X30))</f>
         <v/>
       </c>
+      <c r="AA30" s="28" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr"/>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:39:29</t>
+        </is>
+      </c>
+      <c r="AD30" s="2" t="inlineStr">
+        <is>
+          <t>paquete confirmado | registro definitivo OK (disponibilidad: Lima)</t>
+        </is>
+      </c>
     </row>
     <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>TE-EMP-CM-126</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>Residencial</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>10</v>
+      </c>
+      <c r="J31" s="19" t="inlineStr">
+        <is>
+          <t>https://www.prueba.com</t>
+        </is>
+      </c>
+      <c r="K31" s="19" t="n">
+        <v>14856321</v>
+      </c>
+      <c r="L31" s="19" t="inlineStr">
+        <is>
+          <t>prueba@gmail.com</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>4 servicios: TFP + TVP + IF + SMC</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>TE-TFP-CM-004</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>TE-TVP-CM-004</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>TE-IF-CM-005</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t>TE-SMC-CM-001</t>
+        </is>
+      </c>
       <c r="Z31" s="20">
         <f>IF(C31="","",COUNTA(N31,P31,R31,T31,V31,X31))</f>
         <v/>
       </c>
+      <c r="AA31" s="28" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr"/>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:39:50</t>
+        </is>
+      </c>
+      <c r="AD31" s="2" t="inlineStr">
+        <is>
+          <t>paquete confirmado | registro definitivo OK (disponibilidad: Lima)</t>
+        </is>
+      </c>
     </row>
     <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>TE-EMP-CM-127</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Residencial</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>10</v>
+      </c>
+      <c r="J32" s="19" t="inlineStr">
+        <is>
+          <t>https://www.prueba.com</t>
+        </is>
+      </c>
+      <c r="K32" s="19" t="n">
+        <v>14856321</v>
+      </c>
+      <c r="L32" s="19" t="inlineStr">
+        <is>
+          <t>prueba@gmail.com</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>4 servicios: TFP + TVP + IF + SMO</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>TE-TFP-CM-007</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>TE-TVP-CM-007</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>TE-IF-CM-009</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>TE-SMO-CM-001</t>
+        </is>
+      </c>
       <c r="Z32" s="20">
         <f>IF(C32="","",COUNTA(N32,P32,R32,T32,V32,X32))</f>
         <v/>
       </c>
+      <c r="AA32" s="28" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr"/>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:40:11</t>
+        </is>
+      </c>
+      <c r="AD32" s="2" t="inlineStr">
+        <is>
+          <t>paquete confirmado | registro definitivo OK (disponibilidad: Lima)</t>
+        </is>
+      </c>
     </row>
     <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>TE-EMP-CM-128</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>Residencial</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>10</v>
+      </c>
+      <c r="J33" s="19" t="inlineStr">
+        <is>
+          <t>https://www.prueba.com</t>
+        </is>
+      </c>
+      <c r="K33" s="19" t="n">
+        <v>14856321</v>
+      </c>
+      <c r="L33" s="19" t="inlineStr">
+        <is>
+          <t>prueba@gmail.com</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>4 servicios: TFP + TVP + IF + SMQ</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>TE-TFP-CM-010</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>TE-TVP-CM-010</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr">
+        <is>
+          <t>TE-IF-CM-003</t>
+        </is>
+      </c>
+      <c r="T33" s="2" t="inlineStr">
+        <is>
+          <t>TE-SMQ-CM-001</t>
+        </is>
+      </c>
       <c r="Z33" s="20">
         <f>IF(C33="","",COUNTA(N33,P33,R33,T33,V33,X33))</f>
         <v/>
       </c>
+      <c r="AA33" s="28" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr"/>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:40:32</t>
+        </is>
+      </c>
+      <c r="AD33" s="2" t="inlineStr">
+        <is>
+          <t>paquete confirmado | registro definitivo OK (disponibilidad: Lima)</t>
+        </is>
+      </c>
     </row>
     <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>TE-EMP-CM-129</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Residencial</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>10</v>
+      </c>
+      <c r="J34" s="19" t="inlineStr">
+        <is>
+          <t>https://www.prueba.com</t>
+        </is>
+      </c>
+      <c r="K34" s="19" t="n">
+        <v>14856321</v>
+      </c>
+      <c r="L34" s="19" t="inlineStr">
+        <is>
+          <t>prueba@gmail.com</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>4 servicios: TFP + TVP + PIF + SMP</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>TE-TFP-CM-001</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>TE-TVP-CM-001</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>TE-PIF-CM-003</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>TE-SMP-CM-002</t>
+        </is>
+      </c>
       <c r="Z34" s="20">
         <f>IF(C34="","",COUNTA(N34,P34,R34,T34,V34,X34))</f>
         <v/>
       </c>
+      <c r="AA34" s="28" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr"/>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:40:55</t>
+        </is>
+      </c>
+      <c r="AD34" s="2" t="inlineStr">
+        <is>
+          <t>paquete confirmado | registro definitivo OK (disponibilidad: Lima)</t>
+        </is>
+      </c>
     </row>
     <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>TE-EMP-CM-130</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>Residencial</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>10</v>
+      </c>
+      <c r="J35" s="19" t="inlineStr">
+        <is>
+          <t>https://www.prueba.com</t>
+        </is>
+      </c>
+      <c r="K35" s="19" t="n">
+        <v>14856321</v>
+      </c>
+      <c r="L35" s="19" t="inlineStr">
+        <is>
+          <t>prueba@gmail.com</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>4 servicios: TFP + TVP + PIF + SMC</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>TE-TFP-CM-004</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>TE-TVP-CM-004</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>TE-PIF-CM-005</t>
+        </is>
+      </c>
+      <c r="T35" s="2" t="inlineStr">
+        <is>
+          <t>TE-SMC-CM-002</t>
+        </is>
+      </c>
       <c r="Z35" s="20">
         <f>IF(C35="","",COUNTA(N35,P35,R35,T35,V35,X35))</f>
         <v/>
       </c>
+      <c r="AA35" s="28" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr"/>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:41:16</t>
+        </is>
+      </c>
+      <c r="AD35" s="2" t="inlineStr">
+        <is>
+          <t>paquete confirmado | registro definitivo OK (disponibilidad: Lima)</t>
+        </is>
+      </c>
     </row>
     <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>TE-EMP-CM-131</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Residencial</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>10</v>
+      </c>
+      <c r="J36" s="19" t="inlineStr">
+        <is>
+          <t>https://www.prueba.com</t>
+        </is>
+      </c>
+      <c r="K36" s="19" t="n">
+        <v>14856321</v>
+      </c>
+      <c r="L36" s="19" t="inlineStr">
+        <is>
+          <t>prueba@gmail.com</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>4 servicios: TFP + TVP + PIF + SMO</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>TE-TFP-CM-007</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>TE-TVP-CM-007</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>TE-PIF-CM-009</t>
+        </is>
+      </c>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>TE-SMO-CM-002</t>
+        </is>
+      </c>
       <c r="Z36" s="20">
         <f>IF(C36="","",COUNTA(N36,P36,R36,T36,V36,X36))</f>
         <v/>
       </c>
+      <c r="AA36" s="28" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr"/>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:41:37</t>
+        </is>
+      </c>
+      <c r="AD36" s="2" t="inlineStr">
+        <is>
+          <t>paquete confirmado | registro definitivo OK (disponibilidad: Lima)</t>
+        </is>
+      </c>
     </row>
     <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>TE-EMP-CM-132</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Residencial</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>10</v>
+      </c>
+      <c r="J37" s="19" t="inlineStr">
+        <is>
+          <t>https://www.prueba.com</t>
+        </is>
+      </c>
+      <c r="K37" s="19" t="n">
+        <v>14856321</v>
+      </c>
+      <c r="L37" s="19" t="inlineStr">
+        <is>
+          <t>prueba@gmail.com</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>4 servicios: TFP + TVP + PIF + SMQ</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>TE-TFP-CM-010</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>TE-TVP-CM-010</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>TE-PIF-CM-003</t>
+        </is>
+      </c>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>TE-SMQ-CM-002</t>
+        </is>
+      </c>
       <c r="Z37" s="20">
         <f>IF(C37="","",COUNTA(N37,P37,R37,T37,V37,X37))</f>
         <v/>
       </c>
+      <c r="AA37" s="28" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr"/>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:41:59</t>
+        </is>
+      </c>
+      <c r="AD37" s="2" t="inlineStr">
+        <is>
+          <t>paquete confirmado | registro definitivo OK (disponibilidad: Lima)</t>
+        </is>
+      </c>
     </row>
     <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>TE-EMP-CM-133</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Residencial</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>10</v>
+      </c>
+      <c r="J38" s="19" t="inlineStr">
+        <is>
+          <t>https://www.prueba.com</t>
+        </is>
+      </c>
+      <c r="K38" s="19" t="n">
+        <v>14856321</v>
+      </c>
+      <c r="L38" s="19" t="inlineStr">
+        <is>
+          <t>prueba@gmail.com</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>4 servicios: TFP + TVPR + IF + SMP</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>TE-TFP-CM-001</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>TE-TVPR-CM-001</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>TE-IF-CM-005</t>
+        </is>
+      </c>
+      <c r="T38" s="2" t="inlineStr">
+        <is>
+          <t>TE-SMP-CM-003</t>
+        </is>
+      </c>
       <c r="Z38" s="20">
         <f>IF(C38="","",COUNTA(N38,P38,R38,T38,V38,X38))</f>
         <v/>
       </c>
+      <c r="AA38" s="28" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr"/>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:42:20</t>
+        </is>
+      </c>
+      <c r="AD38" s="2" t="inlineStr">
+        <is>
+          <t>paquete confirmado | registro definitivo OK (disponibilidad: Lima)</t>
+        </is>
+      </c>
     </row>
     <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>TE-EMP-CM-134</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>Residencial</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>10</v>
+      </c>
+      <c r="J39" s="19" t="inlineStr">
+        <is>
+          <t>https://www.prueba.com</t>
+        </is>
+      </c>
+      <c r="K39" s="19" t="n">
+        <v>14856321</v>
+      </c>
+      <c r="L39" s="19" t="inlineStr">
+        <is>
+          <t>prueba@gmail.com</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>4 servicios: TFP + TVPR + IF + SMC</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>TE-TFP-CM-004</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>TE-TVPR-CM-004</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr">
+        <is>
+          <t>TE-IF-CM-009</t>
+        </is>
+      </c>
+      <c r="T39" s="2" t="inlineStr">
+        <is>
+          <t>TE-SMC-CM-003</t>
+        </is>
+      </c>
       <c r="Z39" s="20">
         <f>IF(C39="","",COUNTA(N39,P39,R39,T39,V39,X39))</f>
         <v/>
       </c>
+      <c r="AA39" s="28" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr"/>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:42:41</t>
+        </is>
+      </c>
+      <c r="AD39" s="2" t="inlineStr">
+        <is>
+          <t>paquete confirmado | registro definitivo OK (disponibilidad: Lima)</t>
+        </is>
+      </c>
     </row>
     <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>TE-EMP-CM-135</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Residencial</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>10</v>
+      </c>
+      <c r="J40" s="19" t="inlineStr">
+        <is>
+          <t>https://www.prueba.com</t>
+        </is>
+      </c>
+      <c r="K40" s="19" t="n">
+        <v>14856321</v>
+      </c>
+      <c r="L40" s="19" t="inlineStr">
+        <is>
+          <t>prueba@gmail.com</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>4 servicios: TFP + TVPR + IF + SMO</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>TE-TFP-CM-007</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>TE-TVPR-CM-007</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t>TE-IF-CM-003</t>
+        </is>
+      </c>
+      <c r="T40" s="2" t="inlineStr">
+        <is>
+          <t>TE-SMO-CM-003</t>
+        </is>
+      </c>
       <c r="Z40" s="20">
         <f>IF(C40="","",COUNTA(N40,P40,R40,T40,V40,X40))</f>
         <v/>
       </c>
+      <c r="AA40" s="28" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr"/>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:43:02</t>
+        </is>
+      </c>
+      <c r="AD40" s="2" t="inlineStr">
+        <is>
+          <t>paquete confirmado | registro definitivo OK (disponibilidad: Lima)</t>
+        </is>
+      </c>
     </row>
     <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>TE-EMP-CM-136</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>Residencial</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>10</v>
+      </c>
+      <c r="J41" s="19" t="inlineStr">
+        <is>
+          <t>https://www.prueba.com</t>
+        </is>
+      </c>
+      <c r="K41" s="19" t="n">
+        <v>14856321</v>
+      </c>
+      <c r="L41" s="19" t="inlineStr">
+        <is>
+          <t>prueba@gmail.com</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>4 servicios: TFP + TVPR + IF + SMQ</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>TE-TFP-CM-010</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>TE-TVPR-CM-010</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>TE-IF-CM-005</t>
+        </is>
+      </c>
+      <c r="T41" s="2" t="inlineStr">
+        <is>
+          <t>TE-SMQ-CM-003</t>
+        </is>
+      </c>
       <c r="Z41" s="20">
         <f>IF(C41="","",COUNTA(N41,P41,R41,T41,V41,X41))</f>
         <v/>
       </c>
+      <c r="AA41" s="28" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr"/>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:43:23</t>
+        </is>
+      </c>
+      <c r="AD41" s="2" t="inlineStr">
+        <is>
+          <t>paquete confirmado | registro definitivo OK (disponibilidad: Lima)</t>
+        </is>
+      </c>
     </row>
     <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>TE-EMP-CM-137</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>Residencial</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>10</v>
+      </c>
+      <c r="J42" s="19" t="inlineStr">
+        <is>
+          <t>https://www.prueba.com</t>
+        </is>
+      </c>
+      <c r="K42" s="19" t="n">
+        <v>14856321</v>
+      </c>
+      <c r="L42" s="19" t="inlineStr">
+        <is>
+          <t>prueba@gmail.com</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>4 servicios: TFP + TVPR + PIF + SMP</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>TE-TFP-CM-001</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>TE-TVPR-CM-001</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t>TE-PIF-CM-005</t>
+        </is>
+      </c>
+      <c r="T42" s="2" t="inlineStr">
+        <is>
+          <t>TE-SMP-CM-001</t>
+        </is>
+      </c>
       <c r="Z42" s="20">
         <f>IF(C42="","",COUNTA(N42,P42,R42,T42,V42,X42))</f>
         <v/>
       </c>
+      <c r="AA42" s="28" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr"/>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:43:45</t>
+        </is>
+      </c>
+      <c r="AD42" s="2" t="inlineStr">
+        <is>
+          <t>paquete confirmado | registro definitivo OK (disponibilidad: Lima)</t>
+        </is>
+      </c>
     </row>
     <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>TE-EMP-CM-138</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>Residencial</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>10</v>
+      </c>
+      <c r="J43" s="19" t="inlineStr">
+        <is>
+          <t>https://www.prueba.com</t>
+        </is>
+      </c>
+      <c r="K43" s="19" t="n">
+        <v>14856321</v>
+      </c>
+      <c r="L43" s="19" t="inlineStr">
+        <is>
+          <t>prueba@gmail.com</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>4 servicios: TFP + TVPR + PIF + SMC</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>TE-TFP-CM-004</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>TE-TVPR-CM-004</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t>TE-PIF-CM-009</t>
+        </is>
+      </c>
+      <c r="T43" s="2" t="inlineStr">
+        <is>
+          <t>TE-SMC-CM-001</t>
+        </is>
+      </c>
       <c r="Z43" s="20">
         <f>IF(C43="","",COUNTA(N43,P43,R43,T43,V43,X43))</f>
         <v/>
       </c>
+      <c r="AA43" s="28" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr"/>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:44:06</t>
+        </is>
+      </c>
+      <c r="AD43" s="2" t="inlineStr">
+        <is>
+          <t>paquete confirmado | registro definitivo OK (disponibilidad: Lima)</t>
+        </is>
+      </c>
     </row>
     <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>TE-EMP-CM-139</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Residencial</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>10</v>
+      </c>
+      <c r="J44" s="19" t="inlineStr">
+        <is>
+          <t>https://www.prueba.com</t>
+        </is>
+      </c>
+      <c r="K44" s="19" t="n">
+        <v>14856321</v>
+      </c>
+      <c r="L44" s="19" t="inlineStr">
+        <is>
+          <t>prueba@gmail.com</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>4 servicios: TFP + TVPR + PIF + SMO</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>TE-TFP-CM-007</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>TE-TVPR-CM-007</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr">
+        <is>
+          <t>TE-PIF-CM-003</t>
+        </is>
+      </c>
+      <c r="T44" s="2" t="inlineStr">
+        <is>
+          <t>TE-SMO-CM-001</t>
+        </is>
+      </c>
       <c r="Z44" s="20">
         <f>IF(C44="","",COUNTA(N44,P44,R44,T44,V44,X44))</f>
         <v/>
       </c>
+      <c r="AA44" s="28" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr"/>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:44:27</t>
+        </is>
+      </c>
+      <c r="AD44" s="2" t="inlineStr">
+        <is>
+          <t>paquete confirmado | registro definitivo OK (disponibilidad: Lima)</t>
+        </is>
+      </c>
     </row>
     <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>TE-EMP-CM-140</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>Residencial</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>10</v>
+      </c>
+      <c r="J45" s="19" t="inlineStr">
+        <is>
+          <t>https://www.prueba.com</t>
+        </is>
+      </c>
+      <c r="K45" s="19" t="n">
+        <v>14856321</v>
+      </c>
+      <c r="L45" s="19" t="inlineStr">
+        <is>
+          <t>prueba@gmail.com</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>4 servicios: TFP + TVPR + PIF + SMQ</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>TE-TFP-CM-010</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>TE-TVPR-CM-010</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr">
+        <is>
+          <t>TE-PIF-CM-005</t>
+        </is>
+      </c>
+      <c r="T45" s="2" t="inlineStr">
+        <is>
+          <t>TE-SMQ-CM-001</t>
+        </is>
+      </c>
       <c r="Z45" s="20">
         <f>IF(C45="","",COUNTA(N45,P45,R45,T45,V45,X45))</f>
         <v/>
       </c>
+      <c r="AA45" s="28" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr"/>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:44:48</t>
+        </is>
+      </c>
+      <c r="AD45" s="2" t="inlineStr">
+        <is>
+          <t>paquete confirmado | registro definitivo OK (disponibilidad: Lima)</t>
+        </is>
+      </c>
     </row>
     <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>TE-EMP-CM-141</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>Residencial</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>10</v>
+      </c>
+      <c r="J46" s="19" t="inlineStr">
+        <is>
+          <t>https://www.prueba.com</t>
+        </is>
+      </c>
+      <c r="K46" s="19" t="n">
+        <v>14856321</v>
+      </c>
+      <c r="L46" s="19" t="inlineStr">
+        <is>
+          <t>prueba@gmail.com</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>4 servicios: TFP + PTV + IF + SMP</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>TE-TFP-CM-001</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>TE-PTV-CM-001</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t>TE-IF-CM-009</t>
+        </is>
+      </c>
+      <c r="T46" s="2" t="inlineStr">
+        <is>
+          <t>TE-SMP-CM-002</t>
+        </is>
+      </c>
       <c r="Z46" s="20">
         <f>IF(C46="","",COUNTA(N46,P46,R46,T46,V46,X46))</f>
         <v/>
       </c>
+      <c r="AA46" s="28" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr"/>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:45:09</t>
+        </is>
+      </c>
+      <c r="AD46" s="2" t="inlineStr">
+        <is>
+          <t>paquete confirmado | registro definitivo OK (disponibilidad: Lima)</t>
+        </is>
+      </c>
     </row>
     <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>TE-EMP-CM-142</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>Residencial</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>10</v>
+      </c>
+      <c r="J47" s="19" t="inlineStr">
+        <is>
+          <t>https://www.prueba.com</t>
+        </is>
+      </c>
+      <c r="K47" s="19" t="n">
+        <v>14856321</v>
+      </c>
+      <c r="L47" s="19" t="inlineStr">
+        <is>
+          <t>prueba@gmail.com</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>4 servicios: TFP + PTV + IF + SMC</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>TE-TFP-CM-004</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>TE-PTV-CM-004</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr">
+        <is>
+          <t>TE-IF-CM-003</t>
+        </is>
+      </c>
+      <c r="T47" s="2" t="inlineStr">
+        <is>
+          <t>TE-SMC-CM-002</t>
+        </is>
+      </c>
       <c r="Z47" s="20">
         <f>IF(C47="","",COUNTA(N47,P47,R47,T47,V47,X47))</f>
         <v/>
       </c>
+      <c r="AA47" s="28" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr"/>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:45:30</t>
+        </is>
+      </c>
+      <c r="AD47" s="2" t="inlineStr">
+        <is>
+          <t>paquete confirmado | registro definitivo OK (disponibilidad: Lima)</t>
+        </is>
+      </c>
     </row>
     <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>TE-EMP-CM-143</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>Residencial</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>10</v>
+      </c>
+      <c r="J48" s="19" t="inlineStr">
+        <is>
+          <t>https://www.prueba.com</t>
+        </is>
+      </c>
+      <c r="K48" s="19" t="n">
+        <v>14856321</v>
+      </c>
+      <c r="L48" s="19" t="inlineStr">
+        <is>
+          <t>prueba@gmail.com</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>4 servicios: TFP + PTV + IF + SMO</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>TE-TFP-CM-007</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>TE-PTV-CM-007</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr">
+        <is>
+          <t>TE-IF-CM-005</t>
+        </is>
+      </c>
+      <c r="T48" s="2" t="inlineStr">
+        <is>
+          <t>TE-SMO-CM-002</t>
+        </is>
+      </c>
       <c r="Z48" s="20">
         <f>IF(C48="","",COUNTA(N48,P48,R48,T48,V48,X48))</f>
         <v/>
       </c>
+      <c r="AA48" s="28" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr"/>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:45:51</t>
+        </is>
+      </c>
+      <c r="AD48" s="2" t="inlineStr">
+        <is>
+          <t>paquete confirmado | registro definitivo OK (disponibilidad: Lima)</t>
+        </is>
+      </c>
     </row>
     <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>TE-EMP-CM-144</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>Residencial</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
+        <v>10</v>
+      </c>
+      <c r="J49" s="19" t="inlineStr">
+        <is>
+          <t>https://www.prueba.com</t>
+        </is>
+      </c>
+      <c r="K49" s="19" t="n">
+        <v>14856321</v>
+      </c>
+      <c r="L49" s="19" t="inlineStr">
+        <is>
+          <t>prueba@gmail.com</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>4 servicios: TFP + PTV + IF + SMQ</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>TE-TFP-CM-010</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>TE-PTV-CM-010</t>
+        </is>
+      </c>
+      <c r="R49" s="2" t="inlineStr">
+        <is>
+          <t>TE-IF-CM-009</t>
+        </is>
+      </c>
+      <c r="T49" s="2" t="inlineStr">
+        <is>
+          <t>TE-SMQ-CM-002</t>
+        </is>
+      </c>
       <c r="Z49" s="20">
         <f>IF(C49="","",COUNTA(N49,P49,R49,T49,V49,X49))</f>
         <v/>
       </c>
+      <c r="AA49" s="28" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr"/>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:46:13</t>
+        </is>
+      </c>
+      <c r="AD49" s="2" t="inlineStr">
+        <is>
+          <t>paquete confirmado | registro definitivo OK (disponibilidad: Lima)</t>
+        </is>
+      </c>
     </row>
     <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>TE-EMP-CM-145</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>Residencial</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>10</v>
+      </c>
+      <c r="J50" s="19" t="inlineStr">
+        <is>
+          <t>https://www.prueba.com</t>
+        </is>
+      </c>
+      <c r="K50" s="19" t="n">
+        <v>14856321</v>
+      </c>
+      <c r="L50" s="19" t="inlineStr">
+        <is>
+          <t>prueba@gmail.com</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>4 servicios: TFP + PTV + PIF + SMP</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>TE-TFP-CM-001</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>TE-PTV-CM-001</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr">
+        <is>
+          <t>TE-PIF-CM-009</t>
+        </is>
+      </c>
+      <c r="T50" s="2" t="inlineStr">
+        <is>
+          <t>TE-SMP-CM-003</t>
+        </is>
+      </c>
       <c r="Z50" s="20">
         <f>IF(C50="","",COUNTA(N50,P50,R50,T50,V50,X50))</f>
         <v/>
       </c>
+      <c r="AA50" s="28" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr"/>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:46:34</t>
+        </is>
+      </c>
+      <c r="AD50" s="2" t="inlineStr">
+        <is>
+          <t>paquete confirmado | registro definitivo OK (disponibilidad: Lima)</t>
+        </is>
+      </c>
     </row>
     <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>TE-EMP-CM-146</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>Residencial</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>10</v>
+      </c>
+      <c r="J51" s="19" t="inlineStr">
+        <is>
+          <t>https://www.prueba.com</t>
+        </is>
+      </c>
+      <c r="K51" s="19" t="n">
+        <v>14856321</v>
+      </c>
+      <c r="L51" s="19" t="inlineStr">
+        <is>
+          <t>prueba@gmail.com</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>4 servicios: TFP + PTV + PIF + SMC</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>TE-TFP-CM-004</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>TE-PTV-CM-004</t>
+        </is>
+      </c>
+      <c r="R51" s="2" t="inlineStr">
+        <is>
+          <t>TE-PIF-CM-003</t>
+        </is>
+      </c>
+      <c r="T51" s="2" t="inlineStr">
+        <is>
+          <t>TE-SMC-CM-003</t>
+        </is>
+      </c>
       <c r="Z51" s="20">
         <f>IF(C51="","",COUNTA(N51,P51,R51,T51,V51,X51))</f>
         <v/>
       </c>
+      <c r="AA51" s="28" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr"/>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:46:55</t>
+        </is>
+      </c>
+      <c r="AD51" s="2" t="inlineStr">
+        <is>
+          <t>paquete confirmado | registro definitivo OK (disponibilidad: Lima)</t>
+        </is>
+      </c>
     </row>
     <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>TE-EMP-CM-147</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>Residencial</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>10</v>
+      </c>
+      <c r="J52" s="19" t="inlineStr">
+        <is>
+          <t>https://www.prueba.com</t>
+        </is>
+      </c>
+      <c r="K52" s="19" t="n">
+        <v>14856321</v>
+      </c>
+      <c r="L52" s="19" t="inlineStr">
+        <is>
+          <t>prueba@gmail.com</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>4 servicios: TFP + PTV + PIF + SMO</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>TE-TFP-CM-007</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>TE-PTV-CM-007</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="inlineStr">
+        <is>
+          <t>TE-PIF-CM-005</t>
+        </is>
+      </c>
+      <c r="T52" s="2" t="inlineStr">
+        <is>
+          <t>TE-SMO-CM-003</t>
+        </is>
+      </c>
       <c r="Z52" s="20">
         <f>IF(C52="","",COUNTA(N52,P52,R52,T52,V52,X52))</f>
         <v/>
       </c>
+      <c r="AA52" s="28" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr"/>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:47:16</t>
+        </is>
+      </c>
+      <c r="AD52" s="2" t="inlineStr">
+        <is>
+          <t>paquete confirmado | registro definitivo OK (disponibilidad: Lima)</t>
+        </is>
+      </c>
     </row>
     <row r="53">
+      <c r="A53" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>TE-EMP-CM-148</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>Residencial</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>10</v>
+      </c>
+      <c r="J53" s="19" t="inlineStr">
+        <is>
+          <t>https://www.prueba.com</t>
+        </is>
+      </c>
+      <c r="K53" s="19" t="n">
+        <v>14856321</v>
+      </c>
+      <c r="L53" s="19" t="inlineStr">
+        <is>
+          <t>prueba@gmail.com</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>4 servicios: TFP + PTV + PIF + SMQ</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>TE-TFP-CM-010</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>TE-PTV-CM-010</t>
+        </is>
+      </c>
+      <c r="R53" s="2" t="inlineStr">
+        <is>
+          <t>TE-PIF-CM-009</t>
+        </is>
+      </c>
+      <c r="T53" s="2" t="inlineStr">
+        <is>
+          <t>TE-SMQ-CM-003</t>
+        </is>
+      </c>
       <c r="Z53" s="20">
         <f>IF(C53="","",COUNTA(N53,P53,R53,T53,V53,X53))</f>
         <v/>
       </c>
+      <c r="AA53" s="28" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr"/>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:47:37</t>
+        </is>
+      </c>
+      <c r="AD53" s="2" t="inlineStr">
+        <is>
+          <t>paquete confirmado | registro definitivo OK (disponibilidad: Lima)</t>
+        </is>
+      </c>
     </row>
     <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>TE-EMP-CM-149</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>Residencial</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>10</v>
+      </c>
+      <c r="J54" s="19" t="inlineStr">
+        <is>
+          <t>https://www.prueba.com</t>
+        </is>
+      </c>
+      <c r="K54" s="19" t="n">
+        <v>14856321</v>
+      </c>
+      <c r="L54" s="19" t="inlineStr">
+        <is>
+          <t>prueba@gmail.com</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>4 servicios: OTF + TVP + IF + SMP</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>TE-OTF-CM-001</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>TE-TVP-CM-001</t>
+        </is>
+      </c>
+      <c r="R54" s="2" t="inlineStr">
+        <is>
+          <t>TE-IF-CM-003</t>
+        </is>
+      </c>
+      <c r="T54" s="2" t="inlineStr">
+        <is>
+          <t>TE-SMP-CM-001</t>
+        </is>
+      </c>
       <c r="Z54" s="20">
         <f>IF(C54="","",COUNTA(N54,P54,R54,T54,V54,X54))</f>
         <v/>
       </c>
+      <c r="AA54" s="28" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr"/>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:47:59</t>
+        </is>
+      </c>
+      <c r="AD54" s="2" t="inlineStr">
+        <is>
+          <t>paquete confirmado | registro definitivo OK (disponibilidad: Lima)</t>
+        </is>
+      </c>
     </row>
     <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>TE-EMP-CM-150</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>Residencial</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>10</v>
+      </c>
+      <c r="J55" s="19" t="inlineStr">
+        <is>
+          <t>https://www.prueba.com</t>
+        </is>
+      </c>
+      <c r="K55" s="19" t="n">
+        <v>14856321</v>
+      </c>
+      <c r="L55" s="19" t="inlineStr">
+        <is>
+          <t>prueba@gmail.com</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>4 servicios: OTF + TVP + IF + SMC</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>TE-OTF-CM-004</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>TE-TVP-CM-004</t>
+        </is>
+      </c>
+      <c r="R55" s="2" t="inlineStr">
+        <is>
+          <t>TE-IF-CM-005</t>
+        </is>
+      </c>
+      <c r="T55" s="2" t="inlineStr">
+        <is>
+          <t>TE-SMC-CM-001</t>
+        </is>
+      </c>
       <c r="Z55" s="20">
         <f>IF(C55="","",COUNTA(N55,P55,R55,T55,V55,X55))</f>
         <v/>
       </c>
+      <c r="AA55" s="28" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr"/>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:48:20</t>
+        </is>
+      </c>
+      <c r="AD55" s="2" t="inlineStr">
+        <is>
+          <t>paquete confirmado | registro definitivo OK (disponibilidad: Lima)</t>
+        </is>
+      </c>
     </row>
     <row r="56">
+      <c r="A56" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>TE-EMP-CM-151</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>Residencial</t>
+        </is>
+      </c>
+      <c r="I56" t="n">
+        <v>10</v>
+      </c>
+      <c r="J56" s="19" t="inlineStr">
+        <is>
+          <t>https://www.prueba.com</t>
+        </is>
+      </c>
+      <c r="K56" s="19" t="n">
+        <v>14856321</v>
+      </c>
+      <c r="L56" s="19" t="inlineStr">
+        <is>
+          <t>prueba@gmail.com</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>4 servicios: OTF + TVP + IF + SMO</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>TE-OTF-CM-007</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>TE-TVP-CM-007</t>
+        </is>
+      </c>
+      <c r="R56" s="2" t="inlineStr">
+        <is>
+          <t>TE-IF-CM-009</t>
+        </is>
+      </c>
+      <c r="T56" s="2" t="inlineStr">
+        <is>
+          <t>TE-SMO-CM-001</t>
+        </is>
+      </c>
       <c r="Z56" s="20">
         <f>IF(C56="","",COUNTA(N56,P56,R56,T56,V56,X56))</f>
         <v/>
       </c>
+      <c r="AA56" s="28" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr"/>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:48:41</t>
+        </is>
+      </c>
+      <c r="AD56" s="2" t="inlineStr">
+        <is>
+          <t>paquete confirmado | registro definitivo OK (disponibilidad: Lima)</t>
+        </is>
+      </c>
     </row>
     <row r="57">
+      <c r="A57" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>TE-EMP-CM-152</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>Residencial</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
+        <v>10</v>
+      </c>
+      <c r="J57" s="19" t="inlineStr">
+        <is>
+          <t>https://www.prueba.com</t>
+        </is>
+      </c>
+      <c r="K57" s="19" t="n">
+        <v>14856321</v>
+      </c>
+      <c r="L57" s="19" t="inlineStr">
+        <is>
+          <t>prueba@gmail.com</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>4 servicios: OTF + TVP + IF + SMQ</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>TE-OTF-CM-010</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>TE-TVP-CM-010</t>
+        </is>
+      </c>
+      <c r="R57" s="2" t="inlineStr">
+        <is>
+          <t>TE-IF-CM-003</t>
+        </is>
+      </c>
+      <c r="T57" s="2" t="inlineStr">
+        <is>
+          <t>TE-SMQ-CM-001</t>
+        </is>
+      </c>
       <c r="Z57" s="20">
         <f>IF(C57="","",COUNTA(N57,P57,R57,T57,V57,X57))</f>
         <v/>
       </c>
+      <c r="AA57" s="28" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr"/>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:49:02</t>
+        </is>
+      </c>
+      <c r="AD57" s="2" t="inlineStr">
+        <is>
+          <t>paquete confirmado | registro definitivo OK (disponibilidad: Lima)</t>
+        </is>
+      </c>
     </row>
     <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>TE-EMP-CM-153</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>Residencial</t>
+        </is>
+      </c>
+      <c r="I58" t="n">
+        <v>10</v>
+      </c>
+      <c r="J58" s="19" t="inlineStr">
+        <is>
+          <t>https://www.prueba.com</t>
+        </is>
+      </c>
+      <c r="K58" s="19" t="n">
+        <v>14856321</v>
+      </c>
+      <c r="L58" s="19" t="inlineStr">
+        <is>
+          <t>prueba@gmail.com</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>4 servicios: OTF + TVP + PIF + SMP</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>TE-OTF-CM-001</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>TE-TVP-CM-001</t>
+        </is>
+      </c>
+      <c r="R58" s="2" t="inlineStr">
+        <is>
+          <t>TE-PIF-CM-003</t>
+        </is>
+      </c>
+      <c r="T58" s="2" t="inlineStr">
+        <is>
+          <t>TE-SMP-CM-002</t>
+        </is>
+      </c>
       <c r="Z58" s="20">
         <f>IF(C58="","",COUNTA(N58,P58,R58,T58,V58,X58))</f>
         <v/>
       </c>
+      <c r="AA58" s="28" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr"/>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:49:23</t>
+        </is>
+      </c>
+      <c r="AD58" s="2" t="inlineStr">
+        <is>
+          <t>paquete confirmado | registro definitivo OK (disponibilidad: Lima)</t>
+        </is>
+      </c>
     </row>
     <row r="59">
+      <c r="A59" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>TE-EMP-CM-154</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>Residencial</t>
+        </is>
+      </c>
+      <c r="I59" t="n">
+        <v>10</v>
+      </c>
+      <c r="J59" s="19" t="inlineStr">
+        <is>
+          <t>https://www.prueba.com</t>
+        </is>
+      </c>
+      <c r="K59" s="19" t="n">
+        <v>14856321</v>
+      </c>
+      <c r="L59" s="19" t="inlineStr">
+        <is>
+          <t>prueba@gmail.com</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>4 servicios: OTF + TVP + PIF + SMC</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>TE-OTF-CM-004</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>TE-TVP-CM-004</t>
+        </is>
+      </c>
+      <c r="R59" s="2" t="inlineStr">
+        <is>
+          <t>TE-PIF-CM-005</t>
+        </is>
+      </c>
+      <c r="T59" s="2" t="inlineStr">
+        <is>
+          <t>TE-SMC-CM-002</t>
+        </is>
+      </c>
       <c r="Z59" s="20">
         <f>IF(C59="","",COUNTA(N59,P59,R59,T59,V59,X59))</f>
         <v/>
       </c>
+      <c r="AA59" s="28" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr"/>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:49:44</t>
+        </is>
+      </c>
+      <c r="AD59" s="2" t="inlineStr">
+        <is>
+          <t>paquete confirmado | registro definitivo OK (disponibilidad: Lima)</t>
+        </is>
+      </c>
     </row>
     <row r="60">
+      <c r="A60" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>TE-EMP-CM-155</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>Residencial + Comercial</t>
+        </is>
+      </c>
+      <c r="I60" t="n">
+        <v>10</v>
+      </c>
+      <c r="J60" s="19" t="inlineStr">
+        <is>
+          <t>https://www.prueba.com</t>
+        </is>
+      </c>
+      <c r="K60" s="19" t="n">
+        <v>14856321</v>
+      </c>
+      <c r="L60" s="19" t="inlineStr">
+        <is>
+          <t>prueba@gmail.com</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>4 servicios: OTF + TVP + PIF + SMO (alcance Residencial + Comercial: SMO-005 tiene valor)</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>TE-OTF-CM-003</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>TE-TVP-CM-003</t>
+        </is>
+      </c>
+      <c r="R60" s="2" t="inlineStr">
+        <is>
+          <t>TE-PIF-CM-001</t>
+        </is>
+      </c>
+      <c r="T60" s="2" t="inlineStr">
+        <is>
+          <t>TE-SMO-CM-005</t>
+        </is>
+      </c>
       <c r="Z60" s="20">
         <f>IF(C60="","",COUNTA(N60,P60,R60,T60,V60,X60))</f>
         <v/>
       </c>
+      <c r="AA60" s="28" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr"/>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:50:06</t>
+        </is>
+      </c>
+      <c r="AD60" s="2" t="inlineStr">
+        <is>
+          <t>paquete confirmado | registro definitivo OK (disponibilidad: Lima)</t>
+        </is>
+      </c>
     </row>
     <row r="61">
+      <c r="A61" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>TE-EMP-CM-156</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>Residencial</t>
+        </is>
+      </c>
+      <c r="I61" t="n">
+        <v>10</v>
+      </c>
+      <c r="J61" s="19" t="inlineStr">
+        <is>
+          <t>https://www.prueba.com</t>
+        </is>
+      </c>
+      <c r="K61" s="19" t="n">
+        <v>14856321</v>
+      </c>
+      <c r="L61" s="19" t="inlineStr">
+        <is>
+          <t>prueba@gmail.com</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>4 servicios: OTF + TVP + PIF + SMQ</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>TE-OTF-CM-010</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>TE-TVP-CM-010</t>
+        </is>
+      </c>
+      <c r="R61" s="2" t="inlineStr">
+        <is>
+          <t>TE-PIF-CM-003</t>
+        </is>
+      </c>
+      <c r="T61" s="2" t="inlineStr">
+        <is>
+          <t>TE-SMQ-CM-002</t>
+        </is>
+      </c>
       <c r="Z61" s="20">
         <f>IF(C61="","",COUNTA(N61,P61,R61,T61,V61,X61))</f>
         <v/>
       </c>
+      <c r="AA61" s="28" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr"/>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:50:27</t>
+        </is>
+      </c>
+      <c r="AD61" s="2" t="inlineStr">
+        <is>
+          <t>paquete confirmado | registro definitivo OK (disponibilidad: Lima)</t>
+        </is>
+      </c>
     </row>
     <row r="62">
+      <c r="A62" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>TE-EMP-CM-157</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>Residencial</t>
+        </is>
+      </c>
+      <c r="I62" t="n">
+        <v>10</v>
+      </c>
+      <c r="J62" s="19" t="inlineStr">
+        <is>
+          <t>https://www.prueba.com</t>
+        </is>
+      </c>
+      <c r="K62" s="19" t="n">
+        <v>14856321</v>
+      </c>
+      <c r="L62" s="19" t="inlineStr">
+        <is>
+          <t>prueba@gmail.com</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>4 servicios: OTF + TVPR + IF + SMP</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>TE-OTF-CM-001</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>TE-TVPR-CM-001</t>
+        </is>
+      </c>
+      <c r="R62" s="2" t="inlineStr">
+        <is>
+          <t>TE-IF-CM-005</t>
+        </is>
+      </c>
+      <c r="T62" s="2" t="inlineStr">
+        <is>
+          <t>TE-SMP-CM-003</t>
+        </is>
+      </c>
       <c r="Z62" s="20">
         <f>IF(C62="","",COUNTA(N62,P62,R62,T62,V62,X62))</f>
         <v/>
       </c>
+      <c r="AA62" s="28" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr"/>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:50:49</t>
+        </is>
+      </c>
+      <c r="AD62" s="2" t="inlineStr">
+        <is>
+          <t>paquete confirmado | registro definitivo OK (disponibilidad: Lima)</t>
+        </is>
+      </c>
     </row>
     <row r="63">
+      <c r="A63" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>TE-EMP-CM-158</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>Residencial</t>
+        </is>
+      </c>
+      <c r="I63" t="n">
+        <v>10</v>
+      </c>
+      <c r="J63" s="19" t="inlineStr">
+        <is>
+          <t>https://www.prueba.com</t>
+        </is>
+      </c>
+      <c r="K63" s="19" t="n">
+        <v>14856321</v>
+      </c>
+      <c r="L63" s="19" t="inlineStr">
+        <is>
+          <t>prueba@gmail.com</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>4 servicios: OTF + TVPR + IF + SMC</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>TE-OTF-CM-004</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>TE-TVPR-CM-004</t>
+        </is>
+      </c>
+      <c r="R63" s="2" t="inlineStr">
+        <is>
+          <t>TE-IF-CM-009</t>
+        </is>
+      </c>
+      <c r="T63" s="2" t="inlineStr">
+        <is>
+          <t>TE-SMC-CM-003</t>
+        </is>
+      </c>
       <c r="Z63" s="20">
         <f>IF(C63="","",COUNTA(N63,P63,R63,T63,V63,X63))</f>
         <v/>
       </c>
+      <c r="AA63" s="28" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr"/>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:51:11</t>
+        </is>
+      </c>
+      <c r="AD63" s="2" t="inlineStr">
+        <is>
+          <t>paquete confirmado | registro definitivo OK (disponibilidad: Lima)</t>
+        </is>
+      </c>
     </row>
     <row r="64">
+      <c r="A64" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>TE-EMP-CM-159</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>Residencial</t>
+        </is>
+      </c>
+      <c r="I64" t="n">
+        <v>10</v>
+      </c>
+      <c r="J64" s="19" t="inlineStr">
+        <is>
+          <t>https://www.prueba.com</t>
+        </is>
+      </c>
+      <c r="K64" s="19" t="n">
+        <v>14856321</v>
+      </c>
+      <c r="L64" s="19" t="inlineStr">
+        <is>
+          <t>prueba@gmail.com</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>4 servicios: OTF + TVPR + IF + SMO</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>TE-OTF-CM-007</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>TE-TVPR-CM-007</t>
+        </is>
+      </c>
+      <c r="R64" s="2" t="inlineStr">
+        <is>
+          <t>TE-IF-CM-003</t>
+        </is>
+      </c>
+      <c r="T64" s="2" t="inlineStr">
+        <is>
+          <t>TE-SMO-CM-003</t>
+        </is>
+      </c>
       <c r="Z64" s="20">
         <f>IF(C64="","",COUNTA(N64,P64,R64,T64,V64,X64))</f>
         <v/>
       </c>
+      <c r="AA64" s="28" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr"/>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:51:32</t>
+        </is>
+      </c>
+      <c r="AD64" s="2" t="inlineStr">
+        <is>
+          <t>paquete confirmado | registro definitivo OK (disponibilidad: Lima)</t>
+        </is>
+      </c>
     </row>
     <row r="65">
+      <c r="A65" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>TE-EMP-CM-160</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>Residencial</t>
+        </is>
+      </c>
+      <c r="I65" t="n">
+        <v>10</v>
+      </c>
+      <c r="J65" s="19" t="inlineStr">
+        <is>
+          <t>https://www.prueba.com</t>
+        </is>
+      </c>
+      <c r="K65" s="19" t="n">
+        <v>14856321</v>
+      </c>
+      <c r="L65" s="19" t="inlineStr">
+        <is>
+          <t>prueba@gmail.com</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>4 servicios: OTF + TVPR + IF + SMQ</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>TE-OTF-CM-010</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>TE-TVPR-CM-010</t>
+        </is>
+      </c>
+      <c r="R65" s="2" t="inlineStr">
+        <is>
+          <t>TE-IF-CM-005</t>
+        </is>
+      </c>
+      <c r="T65" s="2" t="inlineStr">
+        <is>
+          <t>TE-SMQ-CM-003</t>
+        </is>
+      </c>
       <c r="Z65" s="20">
         <f>IF(C65="","",COUNTA(N65,P65,R65,T65,V65,X65))</f>
         <v/>
       </c>
+      <c r="AA65" s="28" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr"/>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:51:53</t>
+        </is>
+      </c>
+      <c r="AD65" s="2" t="inlineStr">
+        <is>
+          <t>paquete confirmado | registro definitivo OK (disponibilidad: Lima)</t>
+        </is>
+      </c>
     </row>
     <row r="66">
+      <c r="A66" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>TE-EMP-CM-161</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>Residencial</t>
+        </is>
+      </c>
+      <c r="I66" t="n">
+        <v>10</v>
+      </c>
+      <c r="J66" s="19" t="inlineStr">
+        <is>
+          <t>https://www.prueba.com</t>
+        </is>
+      </c>
+      <c r="K66" s="19" t="n">
+        <v>14856321</v>
+      </c>
+      <c r="L66" s="19" t="inlineStr">
+        <is>
+          <t>prueba@gmail.com</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>4 servicios: OTF + TVPR + PIF + SMP</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>TE-OTF-CM-001</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>TE-TVPR-CM-001</t>
+        </is>
+      </c>
+      <c r="R66" s="2" t="inlineStr">
+        <is>
+          <t>TE-PIF-CM-005</t>
+        </is>
+      </c>
+      <c r="T66" s="2" t="inlineStr">
+        <is>
+          <t>TE-SMP-CM-001</t>
+        </is>
+      </c>
       <c r="Z66" s="20">
         <f>IF(C66="","",COUNTA(N66,P66,R66,T66,V66,X66))</f>
         <v/>
       </c>
+      <c r="AA66" s="28" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr"/>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:52:14</t>
+        </is>
+      </c>
+      <c r="AD66" s="2" t="inlineStr">
+        <is>
+          <t>paquete confirmado | registro definitivo OK (disponibilidad: Lima)</t>
+        </is>
+      </c>
     </row>
     <row r="67">
+      <c r="A67" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>TE-EMP-CM-162</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>Residencial</t>
+        </is>
+      </c>
+      <c r="I67" t="n">
+        <v>10</v>
+      </c>
+      <c r="J67" s="19" t="inlineStr">
+        <is>
+          <t>https://www.prueba.com</t>
+        </is>
+      </c>
+      <c r="K67" s="19" t="n">
+        <v>14856321</v>
+      </c>
+      <c r="L67" s="19" t="inlineStr">
+        <is>
+          <t>prueba@gmail.com</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>4 servicios: OTF + TVPR + PIF + SMC</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>TE-OTF-CM-004</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>TE-TVPR-CM-004</t>
+        </is>
+      </c>
+      <c r="R67" s="2" t="inlineStr">
+        <is>
+          <t>TE-PIF-CM-009</t>
+        </is>
+      </c>
+      <c r="T67" s="2" t="inlineStr">
+        <is>
+          <t>TE-SMC-CM-001</t>
+        </is>
+      </c>
       <c r="Z67" s="20">
         <f>IF(C67="","",COUNTA(N67,P67,R67,T67,V67,X67))</f>
         <v/>
       </c>
+      <c r="AA67" s="28" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr"/>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:52:35</t>
+        </is>
+      </c>
+      <c r="AD67" s="2" t="inlineStr">
+        <is>
+          <t>paquete confirmado | registro definitivo OK (disponibilidad: Lima)</t>
+        </is>
+      </c>
     </row>
     <row r="68">
+      <c r="A68" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>TE-EMP-CM-163</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>Residencial + Comercial</t>
+        </is>
+      </c>
+      <c r="I68" t="n">
+        <v>10</v>
+      </c>
+      <c r="J68" s="19" t="inlineStr">
+        <is>
+          <t>https://www.prueba.com</t>
+        </is>
+      </c>
+      <c r="K68" s="19" t="n">
+        <v>14856321</v>
+      </c>
+      <c r="L68" s="19" t="inlineStr">
+        <is>
+          <t>prueba@gmail.com</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>4 servicios: OTF + TVPR + PIF + SMO (alcance Residencial + Comercial: SMO-005 tiene valor)</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>TE-OTF-CM-009</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>TE-TVPR-CM-009</t>
+        </is>
+      </c>
+      <c r="R68" s="2" t="inlineStr">
+        <is>
+          <t>TE-PIF-CM-001</t>
+        </is>
+      </c>
+      <c r="T68" s="2" t="inlineStr">
+        <is>
+          <t>TE-SMO-CM-005</t>
+        </is>
+      </c>
       <c r="Z68" s="20">
         <f>IF(C68="","",COUNTA(N68,P68,R68,T68,V68,X68))</f>
         <v/>
       </c>
+      <c r="AA68" s="28" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr"/>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:52:56</t>
+        </is>
+      </c>
+      <c r="AD68" s="2" t="inlineStr">
+        <is>
+          <t>paquete confirmado | registro definitivo OK (disponibilidad: Lima)</t>
+        </is>
+      </c>
     </row>
     <row r="69">
+      <c r="A69" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>TE-EMP-CM-164</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>Residencial</t>
+        </is>
+      </c>
+      <c r="I69" t="n">
+        <v>10</v>
+      </c>
+      <c r="J69" s="19" t="inlineStr">
+        <is>
+          <t>https://www.prueba.com</t>
+        </is>
+      </c>
+      <c r="K69" s="19" t="n">
+        <v>14856321</v>
+      </c>
+      <c r="L69" s="19" t="inlineStr">
+        <is>
+          <t>prueba@gmail.com</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>4 servicios: OTF + TVPR + PIF + SMQ</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>TE-OTF-CM-010</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>TE-TVPR-CM-010</t>
+        </is>
+      </c>
+      <c r="R69" s="2" t="inlineStr">
+        <is>
+          <t>TE-PIF-CM-005</t>
+        </is>
+      </c>
+      <c r="T69" s="2" t="inlineStr">
+        <is>
+          <t>TE-SMQ-CM-001</t>
+        </is>
+      </c>
       <c r="Z69" s="20">
         <f>IF(C69="","",COUNTA(N69,P69,R69,T69,V69,X69))</f>
         <v/>
       </c>
+      <c r="AA69" s="28" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr"/>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:53:18</t>
+        </is>
+      </c>
+      <c r="AD69" s="2" t="inlineStr">
+        <is>
+          <t>paquete confirmado | registro definitivo OK (disponibilidad: Lima)</t>
+        </is>
+      </c>
     </row>
     <row r="70">
+      <c r="A70" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>TE-EMP-CM-165</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>Residencial</t>
+        </is>
+      </c>
+      <c r="I70" t="n">
+        <v>10</v>
+      </c>
+      <c r="J70" s="19" t="inlineStr">
+        <is>
+          <t>https://www.prueba.com</t>
+        </is>
+      </c>
+      <c r="K70" s="19" t="n">
+        <v>14856321</v>
+      </c>
+      <c r="L70" s="19" t="inlineStr">
+        <is>
+          <t>prueba@gmail.com</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>4 servicios: OTF + PTV + IF + SMP</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>TE-OTF-CM-001</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>TE-PTV-CM-001</t>
+        </is>
+      </c>
+      <c r="R70" s="2" t="inlineStr">
+        <is>
+          <t>TE-IF-CM-009</t>
+        </is>
+      </c>
+      <c r="T70" s="2" t="inlineStr">
+        <is>
+          <t>TE-SMP-CM-002</t>
+        </is>
+      </c>
       <c r="Z70" s="20">
         <f>IF(C70="","",COUNTA(N70,P70,R70,T70,V70,X70))</f>
         <v/>
       </c>
+      <c r="AA70" s="28" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr"/>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:06:55</t>
+        </is>
+      </c>
+      <c r="AD70" s="2" t="inlineStr">
+        <is>
+          <t>paquete confirmado | registro definitivo OK (disponibilidad: Lima)</t>
+        </is>
+      </c>
     </row>
     <row r="71">
+      <c r="A71" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>TE-EMP-CM-166</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>Residencial</t>
+        </is>
+      </c>
+      <c r="I71" t="n">
+        <v>10</v>
+      </c>
+      <c r="J71" s="19" t="inlineStr">
+        <is>
+          <t>https://www.prueba.com</t>
+        </is>
+      </c>
+      <c r="K71" s="19" t="n">
+        <v>14856321</v>
+      </c>
+      <c r="L71" s="19" t="inlineStr">
+        <is>
+          <t>prueba@gmail.com</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>4 servicios: OTF + PTV + IF + SMC</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>TE-OTF-CM-004</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>TE-PTV-CM-004</t>
+        </is>
+      </c>
+      <c r="R71" s="2" t="inlineStr">
+        <is>
+          <t>TE-IF-CM-003</t>
+        </is>
+      </c>
+      <c r="T71" s="2" t="inlineStr">
+        <is>
+          <t>TE-SMC-CM-002</t>
+        </is>
+      </c>
       <c r="Z71" s="20">
         <f>IF(C71="","",COUNTA(N71,P71,R71,T71,V71,X71))</f>
         <v/>
       </c>
+      <c r="AA71" s="28" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr"/>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:21:47</t>
+        </is>
+      </c>
+      <c r="AD71" s="2" t="inlineStr">
+        <is>
+          <t>paquete confirmado | registro definitivo OK (disponibilidad: Lima)</t>
+        </is>
+      </c>
     </row>
     <row r="72">
+      <c r="A72" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>TE-EMP-CM-167</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>Residencial</t>
+        </is>
+      </c>
+      <c r="I72" t="n">
+        <v>10</v>
+      </c>
+      <c r="J72" s="19" t="inlineStr">
+        <is>
+          <t>https://www.prueba.com</t>
+        </is>
+      </c>
+      <c r="K72" s="19" t="n">
+        <v>14856321</v>
+      </c>
+      <c r="L72" s="19" t="inlineStr">
+        <is>
+          <t>prueba@gmail.com</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>4 servicios: OTF + PTV + IF + SMO</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>TE-OTF-CM-007</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>TE-PTV-CM-007</t>
+        </is>
+      </c>
+      <c r="R72" s="2" t="inlineStr">
+        <is>
+          <t>TE-IF-CM-005</t>
+        </is>
+      </c>
+      <c r="T72" s="2" t="inlineStr">
+        <is>
+          <t>TE-SMO-CM-002</t>
+        </is>
+      </c>
       <c r="Z72" s="20">
         <f>IF(C72="","",COUNTA(N72,P72,R72,T72,V72,X72))</f>
         <v/>
       </c>
+      <c r="AA72" s="28" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr"/>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:22:08</t>
+        </is>
+      </c>
+      <c r="AD72" s="2" t="inlineStr">
+        <is>
+          <t>paquete confirmado | registro definitivo OK (disponibilidad: Lima)</t>
+        </is>
+      </c>
     </row>
     <row r="73">
+      <c r="A73" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>TE-EMP-CM-168</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>Residencial</t>
+        </is>
+      </c>
+      <c r="I73" t="n">
+        <v>10</v>
+      </c>
+      <c r="J73" s="19" t="inlineStr">
+        <is>
+          <t>https://www.prueba.com</t>
+        </is>
+      </c>
+      <c r="K73" s="19" t="n">
+        <v>14856321</v>
+      </c>
+      <c r="L73" s="19" t="inlineStr">
+        <is>
+          <t>prueba@gmail.com</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>4 servicios: OTF + PTV + IF + SMQ</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>TE-OTF-CM-010</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>TE-PTV-CM-010</t>
+        </is>
+      </c>
+      <c r="R73" s="2" t="inlineStr">
+        <is>
+          <t>TE-IF-CM-009</t>
+        </is>
+      </c>
+      <c r="T73" s="2" t="inlineStr">
+        <is>
+          <t>TE-SMQ-CM-002</t>
+        </is>
+      </c>
       <c r="Z73" s="20">
         <f>IF(C73="","",COUNTA(N73,P73,R73,T73,V73,X73))</f>
         <v/>
       </c>
+      <c r="AA73" s="28" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr"/>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:22:30</t>
+        </is>
+      </c>
+      <c r="AD73" s="2" t="inlineStr">
+        <is>
+          <t>paquete confirmado | registro definitivo OK (disponibilidad: Lima)</t>
+        </is>
+      </c>
     </row>
     <row r="74">
+      <c r="A74" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>TE-EMP-CM-169</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>Residencial</t>
+        </is>
+      </c>
+      <c r="I74" t="n">
+        <v>10</v>
+      </c>
+      <c r="J74" s="19" t="inlineStr">
+        <is>
+          <t>https://www.prueba.com</t>
+        </is>
+      </c>
+      <c r="K74" s="19" t="n">
+        <v>14856321</v>
+      </c>
+      <c r="L74" s="19" t="inlineStr">
+        <is>
+          <t>prueba@gmail.com</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>4 servicios: OTF + PTV + PIF + SMP</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>TE-OTF-CM-001</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>TE-PTV-CM-001</t>
+        </is>
+      </c>
+      <c r="R74" s="2" t="inlineStr">
+        <is>
+          <t>TE-PIF-CM-009</t>
+        </is>
+      </c>
+      <c r="T74" s="2" t="inlineStr">
+        <is>
+          <t>TE-SMP-CM-003</t>
+        </is>
+      </c>
       <c r="Z74" s="20">
         <f>IF(C74="","",COUNTA(N74,P74,R74,T74,V74,X74))</f>
         <v/>
       </c>
+      <c r="AA74" s="28" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr"/>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:22:51</t>
+        </is>
+      </c>
+      <c r="AD74" s="2" t="inlineStr">
+        <is>
+          <t>paquete confirmado | registro definitivo OK (disponibilidad: Lima)</t>
+        </is>
+      </c>
     </row>
     <row r="75">
+      <c r="A75" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>TE-EMP-CM-170</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>Residencial</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>10</v>
+      </c>
+      <c r="J75" s="19" t="inlineStr">
+        <is>
+          <t>https://www.prueba.com</t>
+        </is>
+      </c>
+      <c r="K75" s="19" t="n">
+        <v>14856321</v>
+      </c>
+      <c r="L75" s="19" t="inlineStr">
+        <is>
+          <t>prueba@gmail.com</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>4 servicios: OTF + PTV + PIF + SMC</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>TE-OTF-CM-004</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>TE-PTV-CM-004</t>
+        </is>
+      </c>
+      <c r="R75" s="2" t="inlineStr">
+        <is>
+          <t>TE-PIF-CM-003</t>
+        </is>
+      </c>
+      <c r="T75" s="2" t="inlineStr">
+        <is>
+          <t>TE-SMC-CM-003</t>
+        </is>
+      </c>
       <c r="Z75" s="20">
         <f>IF(C75="","",COUNTA(N75,P75,R75,T75,V75,X75))</f>
         <v/>
       </c>
+      <c r="AA75" s="28" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr"/>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:23:12</t>
+        </is>
+      </c>
+      <c r="AD75" s="2" t="inlineStr">
+        <is>
+          <t>paquete confirmado | registro definitivo OK (disponibilidad: Lima)</t>
+        </is>
+      </c>
     </row>
     <row r="76">
+      <c r="A76" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>TE-EMP-CM-171</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>Residencial + Comercial</t>
+        </is>
+      </c>
+      <c r="I76" t="n">
+        <v>10</v>
+      </c>
+      <c r="J76" s="19" t="inlineStr">
+        <is>
+          <t>https://www.prueba.com</t>
+        </is>
+      </c>
+      <c r="K76" s="19" t="n">
+        <v>14856321</v>
+      </c>
+      <c r="L76" s="19" t="inlineStr">
+        <is>
+          <t>prueba@gmail.com</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>4 servicios: OTF + PTV + PIF + SMO (alcance Residencial + Comercial: SMO-005 tiene valor)</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>TE-OTF-CM-006</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>TE-PTV-CM-006</t>
+        </is>
+      </c>
+      <c r="R76" s="2" t="inlineStr">
+        <is>
+          <t>TE-PIF-CM-001</t>
+        </is>
+      </c>
+      <c r="T76" s="2" t="inlineStr">
+        <is>
+          <t>TE-SMO-CM-005</t>
+        </is>
+      </c>
       <c r="Z76" s="20">
         <f>IF(C76="","",COUNTA(N76,P76,R76,T76,V76,X76))</f>
         <v/>
       </c>
+      <c r="AA76" s="28" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr"/>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:23:33</t>
+        </is>
+      </c>
+      <c r="AD76" s="2" t="inlineStr">
+        <is>
+          <t>paquete confirmado | registro definitivo OK (disponibilidad: Lima)</t>
+        </is>
+      </c>
     </row>
     <row r="77">
+      <c r="A77" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>TE-EMP-CM-172</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>Residencial</t>
+        </is>
+      </c>
+      <c r="I77" t="n">
+        <v>10</v>
+      </c>
+      <c r="J77" s="19" t="inlineStr">
+        <is>
+          <t>https://www.prueba.com</t>
+        </is>
+      </c>
+      <c r="K77" s="19" t="n">
+        <v>14856321</v>
+      </c>
+      <c r="L77" s="19" t="inlineStr">
+        <is>
+          <t>prueba@gmail.com</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>4 servicios: OTF + PTV + PIF + SMQ</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>TE-OTF-CM-010</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>TE-PTV-CM-010</t>
+        </is>
+      </c>
+      <c r="R77" s="2" t="inlineStr">
+        <is>
+          <t>TE-PIF-CM-009</t>
+        </is>
+      </c>
+      <c r="T77" s="2" t="inlineStr">
+        <is>
+          <t>TE-SMQ-CM-003</t>
+        </is>
+      </c>
       <c r="Z77" s="20">
         <f>IF(C77="","",COUNTA(N77,P77,R77,T77,V77,X77))</f>
         <v/>
       </c>
+      <c r="AA77" s="28" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr"/>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:23:54</t>
+        </is>
+      </c>
+      <c r="AD77" s="2" t="inlineStr">
+        <is>
+          <t>paquete confirmado | registro definitivo OK (disponibilidad: Lima)</t>
+        </is>
+      </c>
     </row>
     <row r="78">
+      <c r="A78" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>TE-EMP-CM-173</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>Residencial</t>
+        </is>
+      </c>
+      <c r="I78" t="n">
+        <v>10</v>
+      </c>
+      <c r="J78" s="19" t="inlineStr">
+        <is>
+          <t>https://www.prueba.com</t>
+        </is>
+      </c>
+      <c r="K78" s="19" t="n">
+        <v>14856321</v>
+      </c>
+      <c r="L78" s="19" t="inlineStr">
+        <is>
+          <t>prueba@gmail.com</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>4 servicios: PTF + TVP + IF + SMP</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>TE-PTF-CM-001</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>TE-TVP-CM-001</t>
+        </is>
+      </c>
+      <c r="R78" s="2" t="inlineStr">
+        <is>
+          <t>TE-IF-CM-003</t>
+        </is>
+      </c>
+      <c r="T78" s="2" t="inlineStr">
+        <is>
+          <t>TE-SMP-CM-001</t>
+        </is>
+      </c>
       <c r="Z78" s="20">
         <f>IF(C78="","",COUNTA(N78,P78,R78,T78,V78,X78))</f>
         <v/>
       </c>
+      <c r="AA78" s="28" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr"/>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:24:15</t>
+        </is>
+      </c>
+      <c r="AD78" s="2" t="inlineStr">
+        <is>
+          <t>paquete confirmado | registro definitivo OK (disponibilidad: Lima)</t>
+        </is>
+      </c>
     </row>
     <row r="79">
+      <c r="A79" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>TE-EMP-CM-174</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>Residencial</t>
+        </is>
+      </c>
+      <c r="I79" t="n">
+        <v>10</v>
+      </c>
+      <c r="J79" s="19" t="inlineStr">
+        <is>
+          <t>https://www.prueba.com</t>
+        </is>
+      </c>
+      <c r="K79" s="19" t="n">
+        <v>14856321</v>
+      </c>
+      <c r="L79" s="19" t="inlineStr">
+        <is>
+          <t>prueba@gmail.com</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>4 servicios: PTF + TVP + IF + SMC</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>TE-PTF-CM-004</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>TE-TVP-CM-004</t>
+        </is>
+      </c>
+      <c r="R79" s="2" t="inlineStr">
+        <is>
+          <t>TE-IF-CM-005</t>
+        </is>
+      </c>
+      <c r="T79" s="2" t="inlineStr">
+        <is>
+          <t>TE-SMC-CM-001</t>
+        </is>
+      </c>
       <c r="Z79" s="20">
         <f>IF(C79="","",COUNTA(N79,P79,R79,T79,V79,X79))</f>
         <v/>
       </c>
+      <c r="AA79" s="28" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr"/>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:24:36</t>
+        </is>
+      </c>
+      <c r="AD79" s="2" t="inlineStr">
+        <is>
+          <t>paquete confirmado | registro definitivo OK (disponibilidad: Lima)</t>
+        </is>
+      </c>
     </row>
     <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>TE-EMP-CM-175</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>Residencial</t>
+        </is>
+      </c>
+      <c r="I80" t="n">
+        <v>10</v>
+      </c>
+      <c r="J80" s="19" t="inlineStr">
+        <is>
+          <t>https://www.prueba.com</t>
+        </is>
+      </c>
+      <c r="K80" s="19" t="n">
+        <v>14856321</v>
+      </c>
+      <c r="L80" s="19" t="inlineStr">
+        <is>
+          <t>prueba@gmail.com</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>4 servicios: PTF + TVP + IF + SMO</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>TE-PTF-CM-007</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>TE-TVP-CM-007</t>
+        </is>
+      </c>
+      <c r="R80" s="2" t="inlineStr">
+        <is>
+          <t>TE-IF-CM-009</t>
+        </is>
+      </c>
+      <c r="T80" s="2" t="inlineStr">
+        <is>
+          <t>TE-SMO-CM-001</t>
+        </is>
+      </c>
       <c r="Z80" s="20">
         <f>IF(C80="","",COUNTA(N80,P80,R80,T80,V80,X80))</f>
         <v/>
       </c>
+      <c r="AA80" s="28" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr"/>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:24:57</t>
+        </is>
+      </c>
+      <c r="AD80" s="2" t="inlineStr">
+        <is>
+          <t>paquete confirmado | registro definitivo OK (disponibilidad: Lima)</t>
+        </is>
+      </c>
     </row>
     <row r="81">
+      <c r="A81" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>TE-EMP-CM-176</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>Residencial</t>
+        </is>
+      </c>
+      <c r="I81" t="n">
+        <v>10</v>
+      </c>
+      <c r="J81" s="19" t="inlineStr">
+        <is>
+          <t>https://www.prueba.com</t>
+        </is>
+      </c>
+      <c r="K81" s="19" t="n">
+        <v>14856321</v>
+      </c>
+      <c r="L81" s="19" t="inlineStr">
+        <is>
+          <t>prueba@gmail.com</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>4 servicios: PTF + TVP + IF + SMQ</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>TE-PTF-CM-010</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>TE-TVP-CM-010</t>
+        </is>
+      </c>
+      <c r="R81" s="2" t="inlineStr">
+        <is>
+          <t>TE-IF-CM-003</t>
+        </is>
+      </c>
+      <c r="T81" s="2" t="inlineStr">
+        <is>
+          <t>TE-SMQ-CM-001</t>
+        </is>
+      </c>
       <c r="Z81" s="20">
         <f>IF(C81="","",COUNTA(N81,P81,R81,T81,V81,X81))</f>
         <v/>
       </c>
+      <c r="AA81" s="28" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr"/>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:25:19</t>
+        </is>
+      </c>
+      <c r="AD81" s="2" t="inlineStr">
+        <is>
+          <t>paquete confirmado | registro definitivo OK (disponibilidad: Lima)</t>
+        </is>
+      </c>
     </row>
     <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>77</v>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>TE-EMP-CM-177</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>Residencial</t>
+        </is>
+      </c>
+      <c r="I82" t="n">
+        <v>10</v>
+      </c>
+      <c r="J82" s="19" t="inlineStr">
+        <is>
+          <t>https://www.prueba.com</t>
+        </is>
+      </c>
+      <c r="K82" s="19" t="n">
+        <v>14856321</v>
+      </c>
+      <c r="L82" s="19" t="inlineStr">
+        <is>
+          <t>prueba@gmail.com</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>4 servicios: PTF + TVP + PIF + SMP</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>TE-PTF-CM-001</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>TE-TVP-CM-001</t>
+        </is>
+      </c>
+      <c r="R82" s="2" t="inlineStr">
+        <is>
+          <t>TE-PIF-CM-003</t>
+        </is>
+      </c>
+      <c r="T82" s="2" t="inlineStr">
+        <is>
+          <t>TE-SMP-CM-002</t>
+        </is>
+      </c>
       <c r="Z82" s="20">
         <f>IF(C82="","",COUNTA(N82,P82,R82,T82,V82,X82))</f>
         <v/>
       </c>
+      <c r="AA82" s="28" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr"/>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:25:40</t>
+        </is>
+      </c>
+      <c r="AD82" s="2" t="inlineStr">
+        <is>
+          <t>paquete confirmado | registro definitivo OK (disponibilidad: Lima)</t>
+        </is>
+      </c>
     </row>
     <row r="83">
+      <c r="A83" s="2" t="n">
+        <v>78</v>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>TE-EMP-CM-178</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>Residencial</t>
+        </is>
+      </c>
+      <c r="I83" t="n">
+        <v>10</v>
+      </c>
+      <c r="J83" s="19" t="inlineStr">
+        <is>
+          <t>https://www.prueba.com</t>
+        </is>
+      </c>
+      <c r="K83" s="19" t="n">
+        <v>14856321</v>
+      </c>
+      <c r="L83" s="19" t="inlineStr">
+        <is>
+          <t>prueba@gmail.com</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>4 servicios: PTF + TVP + PIF + SMC</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>TE-PTF-CM-004</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>TE-TVP-CM-004</t>
+        </is>
+      </c>
+      <c r="R83" s="2" t="inlineStr">
+        <is>
+          <t>TE-PIF-CM-005</t>
+        </is>
+      </c>
+      <c r="T83" s="2" t="inlineStr">
+        <is>
+          <t>TE-SMC-CM-002</t>
+        </is>
+      </c>
       <c r="Z83" s="20">
         <f>IF(C83="","",COUNTA(N83,P83,R83,T83,V83,X83))</f>
         <v/>
       </c>
+      <c r="AA83" s="28" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr"/>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:26:01</t>
+        </is>
+      </c>
+      <c r="AD83" s="2" t="inlineStr">
+        <is>
+          <t>paquete confirmado | registro definitivo OK (disponibilidad: Lima)</t>
+        </is>
+      </c>
     </row>
     <row r="84">
+      <c r="A84" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>TE-EMP-CM-179</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>Residencial + Comercial</t>
+        </is>
+      </c>
+      <c r="I84" t="n">
+        <v>10</v>
+      </c>
+      <c r="J84" s="19" t="inlineStr">
+        <is>
+          <t>https://www.prueba.com</t>
+        </is>
+      </c>
+      <c r="K84" s="19" t="n">
+        <v>14856321</v>
+      </c>
+      <c r="L84" s="19" t="inlineStr">
+        <is>
+          <t>prueba@gmail.com</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>4 servicios: PTF + TVP + PIF + SMO (alcance Residencial + Comercial: SMO-005 tiene valor)</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>TE-PTF-CM-003</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>TE-TVP-CM-003</t>
+        </is>
+      </c>
+      <c r="R84" s="2" t="inlineStr">
+        <is>
+          <t>TE-PIF-CM-001</t>
+        </is>
+      </c>
+      <c r="T84" s="2" t="inlineStr">
+        <is>
+          <t>TE-SMO-CM-005</t>
+        </is>
+      </c>
       <c r="Z84" s="20">
         <f>IF(C84="","",COUNTA(N84,P84,R84,T84,V84,X84))</f>
         <v/>
       </c>
+      <c r="AA84" s="28" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr"/>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:26:22</t>
+        </is>
+      </c>
+      <c r="AD84" s="2" t="inlineStr">
+        <is>
+          <t>paquete confirmado | registro definitivo OK (disponibilidad: Lima)</t>
+        </is>
+      </c>
     </row>
     <row r="85">
+      <c r="A85" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>TE-EMP-CM-180</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>Residencial</t>
+        </is>
+      </c>
+      <c r="I85" t="n">
+        <v>10</v>
+      </c>
+      <c r="J85" s="19" t="inlineStr">
+        <is>
+          <t>https://www.prueba.com</t>
+        </is>
+      </c>
+      <c r="K85" s="19" t="n">
+        <v>14856321</v>
+      </c>
+      <c r="L85" s="19" t="inlineStr">
+        <is>
+          <t>prueba@gmail.com</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>4 servicios: PTF + TVP + PIF + SMQ</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>TE-PTF-CM-010</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>TE-TVP-CM-010</t>
+        </is>
+      </c>
+      <c r="R85" s="2" t="inlineStr">
+        <is>
+          <t>TE-PIF-CM-003</t>
+        </is>
+      </c>
+      <c r="T85" s="2" t="inlineStr">
+        <is>
+          <t>TE-SMQ-CM-002</t>
+        </is>
+      </c>
       <c r="Z85" s="20">
         <f>IF(C85="","",COUNTA(N85,P85,R85,T85,V85,X85))</f>
         <v/>
       </c>
+      <c r="AA85" s="28" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr"/>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:26:43</t>
+        </is>
+      </c>
+      <c r="AD85" s="2" t="inlineStr">
+        <is>
+          <t>paquete confirmado | registro definitivo OK (disponibilidad: Lima)</t>
+        </is>
+      </c>
     </row>
     <row r="86">
+      <c r="A86" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>TE-EMP-CM-181</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>Residencial</t>
+        </is>
+      </c>
+      <c r="I86" t="n">
+        <v>10</v>
+      </c>
+      <c r="J86" s="19" t="inlineStr">
+        <is>
+          <t>https://www.prueba.com</t>
+        </is>
+      </c>
+      <c r="K86" s="19" t="n">
+        <v>14856321</v>
+      </c>
+      <c r="L86" s="19" t="inlineStr">
+        <is>
+          <t>prueba@gmail.com</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>4 servicios: PTF + TVPR + IF + SMP</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>TE-PTF-CM-001</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>TE-TVPR-CM-001</t>
+        </is>
+      </c>
+      <c r="R86" s="2" t="inlineStr">
+        <is>
+          <t>TE-IF-CM-005</t>
+        </is>
+      </c>
+      <c r="T86" s="2" t="inlineStr">
+        <is>
+          <t>TE-SMP-CM-003</t>
+        </is>
+      </c>
       <c r="Z86" s="20">
         <f>IF(C86="","",COUNTA(N86,P86,R86,T86,V86,X86))</f>
         <v/>
       </c>
+      <c r="AA86" s="28" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr"/>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:27:04</t>
+        </is>
+      </c>
+      <c r="AD86" s="2" t="inlineStr">
+        <is>
+          <t>paquete confirmado | registro definitivo OK (disponibilidad: Lima)</t>
+        </is>
+      </c>
     </row>
     <row r="87">
+      <c r="A87" s="2" t="n">
+        <v>82</v>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>TE-EMP-CM-182</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>Residencial</t>
+        </is>
+      </c>
+      <c r="I87" t="n">
+        <v>10</v>
+      </c>
+      <c r="J87" s="19" t="inlineStr">
+        <is>
+          <t>https://www.prueba.com</t>
+        </is>
+      </c>
+      <c r="K87" s="19" t="n">
+        <v>14856321</v>
+      </c>
+      <c r="L87" s="19" t="inlineStr">
+        <is>
+          <t>prueba@gmail.com</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>4 servicios: PTF + TVPR + IF + SMC</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>TE-PTF-CM-004</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>TE-TVPR-CM-004</t>
+        </is>
+      </c>
+      <c r="R87" s="2" t="inlineStr">
+        <is>
+          <t>TE-IF-CM-009</t>
+        </is>
+      </c>
+      <c r="T87" s="2" t="inlineStr">
+        <is>
+          <t>TE-SMC-CM-003</t>
+        </is>
+      </c>
       <c r="Z87" s="20">
         <f>IF(C87="","",COUNTA(N87,P87,R87,T87,V87,X87))</f>
         <v/>
       </c>
+      <c r="AA87" s="28" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr"/>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:27:26</t>
+        </is>
+      </c>
+      <c r="AD87" s="2" t="inlineStr">
+        <is>
+          <t>paquete confirmado | registro definitivo OK (disponibilidad: Lima)</t>
+        </is>
+      </c>
     </row>
     <row r="88">
+      <c r="A88" s="2" t="n">
+        <v>83</v>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>TE-EMP-CM-183</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>Residencial</t>
+        </is>
+      </c>
+      <c r="I88" t="n">
+        <v>10</v>
+      </c>
+      <c r="J88" s="19" t="inlineStr">
+        <is>
+          <t>https://www.prueba.com</t>
+        </is>
+      </c>
+      <c r="K88" s="19" t="n">
+        <v>14856321</v>
+      </c>
+      <c r="L88" s="19" t="inlineStr">
+        <is>
+          <t>prueba@gmail.com</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>4 servicios: PTF + TVPR + IF + SMO</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>TE-PTF-CM-007</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>TE-TVPR-CM-007</t>
+        </is>
+      </c>
+      <c r="R88" s="2" t="inlineStr">
+        <is>
+          <t>TE-IF-CM-003</t>
+        </is>
+      </c>
+      <c r="T88" s="2" t="inlineStr">
+        <is>
+          <t>TE-SMO-CM-003</t>
+        </is>
+      </c>
       <c r="Z88" s="20">
         <f>IF(C88="","",COUNTA(N88,P88,R88,T88,V88,X88))</f>
         <v/>
       </c>
+      <c r="AA88" s="28" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr"/>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:27:47</t>
+        </is>
+      </c>
+      <c r="AD88" s="2" t="inlineStr">
+        <is>
+          <t>paquete confirmado | registro definitivo OK (disponibilidad: Lima)</t>
+        </is>
+      </c>
     </row>
     <row r="89">
+      <c r="A89" s="2" t="n">
+        <v>84</v>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>TE-EMP-CM-184</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>Residencial</t>
+        </is>
+      </c>
+      <c r="I89" t="n">
+        <v>10</v>
+      </c>
+      <c r="J89" s="19" t="inlineStr">
+        <is>
+          <t>https://www.prueba.com</t>
+        </is>
+      </c>
+      <c r="K89" s="19" t="n">
+        <v>14856321</v>
+      </c>
+      <c r="L89" s="19" t="inlineStr">
+        <is>
+          <t>prueba@gmail.com</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>4 servicios: PTF + TVPR + IF + SMQ</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>TE-PTF-CM-010</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>TE-TVPR-CM-010</t>
+        </is>
+      </c>
+      <c r="R89" s="2" t="inlineStr">
+        <is>
+          <t>TE-IF-CM-005</t>
+        </is>
+      </c>
+      <c r="T89" s="2" t="inlineStr">
+        <is>
+          <t>TE-SMQ-CM-003</t>
+        </is>
+      </c>
       <c r="Z89" s="20">
         <f>IF(C89="","",COUNTA(N89,P89,R89,T89,V89,X89))</f>
         <v/>
       </c>
+      <c r="AA89" s="28" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr"/>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:28:08</t>
+        </is>
+      </c>
+      <c r="AD89" s="2" t="inlineStr">
+        <is>
+          <t>paquete confirmado | registro definitivo OK (disponibilidad: Lima)</t>
+        </is>
+      </c>
     </row>
     <row r="90">
+      <c r="A90" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>TE-EMP-CM-185</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>Residencial</t>
+        </is>
+      </c>
+      <c r="I90" t="n">
+        <v>10</v>
+      </c>
+      <c r="J90" s="19" t="inlineStr">
+        <is>
+          <t>https://www.prueba.com</t>
+        </is>
+      </c>
+      <c r="K90" s="19" t="n">
+        <v>14856321</v>
+      </c>
+      <c r="L90" s="19" t="inlineStr">
+        <is>
+          <t>prueba@gmail.com</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>4 servicios: PTF + TVPR + PIF + SMP</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>TE-PTF-CM-001</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>TE-TVPR-CM-001</t>
+        </is>
+      </c>
+      <c r="R90" s="2" t="inlineStr">
+        <is>
+          <t>TE-PIF-CM-005</t>
+        </is>
+      </c>
+      <c r="T90" s="2" t="inlineStr">
+        <is>
+          <t>TE-SMP-CM-001</t>
+        </is>
+      </c>
       <c r="Z90" s="20">
         <f>IF(C90="","",COUNTA(N90,P90,R90,T90,V90,X90))</f>
         <v/>
       </c>
+      <c r="AA90" s="28" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr"/>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:28:29</t>
+        </is>
+      </c>
+      <c r="AD90" s="2" t="inlineStr">
+        <is>
+          <t>paquete confirmado | registro definitivo OK (disponibilidad: Lima)</t>
+        </is>
+      </c>
     </row>
     <row r="91">
+      <c r="A91" s="2" t="n">
+        <v>86</v>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>TE-EMP-CM-186</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>Residencial</t>
+        </is>
+      </c>
+      <c r="I91" t="n">
+        <v>10</v>
+      </c>
+      <c r="J91" s="19" t="inlineStr">
+        <is>
+          <t>https://www.prueba.com</t>
+        </is>
+      </c>
+      <c r="K91" s="19" t="n">
+        <v>14856321</v>
+      </c>
+      <c r="L91" s="19" t="inlineStr">
+        <is>
+          <t>prueba@gmail.com</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>4 servicios: PTF + TVPR + PIF + SMC</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>TE-PTF-CM-004</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>TE-TVPR-CM-004</t>
+        </is>
+      </c>
+      <c r="R91" s="2" t="inlineStr">
+        <is>
+          <t>TE-PIF-CM-009</t>
+        </is>
+      </c>
+      <c r="T91" s="2" t="inlineStr">
+        <is>
+          <t>TE-SMC-CM-001</t>
+        </is>
+      </c>
       <c r="Z91" s="20">
         <f>IF(C91="","",COUNTA(N91,P91,R91,T91,V91,X91))</f>
         <v/>
       </c>
+      <c r="AA91" s="28" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr"/>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:28:50</t>
+        </is>
+      </c>
+      <c r="AD91" s="2" t="inlineStr">
+        <is>
+          <t>paquete confirmado | registro definitivo OK (disponibilidad: Lima)</t>
+        </is>
+      </c>
     </row>
     <row r="92">
+      <c r="A92" s="2" t="n">
+        <v>87</v>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>TE-EMP-CM-187</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>Residencial + Comercial</t>
+        </is>
+      </c>
+      <c r="I92" t="n">
+        <v>10</v>
+      </c>
+      <c r="J92" s="19" t="inlineStr">
+        <is>
+          <t>https://www.prueba.com</t>
+        </is>
+      </c>
+      <c r="K92" s="19" t="n">
+        <v>14856321</v>
+      </c>
+      <c r="L92" s="19" t="inlineStr">
+        <is>
+          <t>prueba@gmail.com</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>4 servicios: PTF + TVPR + PIF + SMO (alcance Residencial + Comercial: SMO-005 tiene valor)</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>TE-PTF-CM-009</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>TE-TVPR-CM-009</t>
+        </is>
+      </c>
+      <c r="R92" s="2" t="inlineStr">
+        <is>
+          <t>TE-PIF-CM-001</t>
+        </is>
+      </c>
+      <c r="T92" s="2" t="inlineStr">
+        <is>
+          <t>TE-SMO-CM-005</t>
+        </is>
+      </c>
       <c r="Z92" s="20">
         <f>IF(C92="","",COUNTA(N92,P92,R92,T92,V92,X92))</f>
         <v/>
       </c>
+      <c r="AA92" s="28" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr"/>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:29:11</t>
+        </is>
+      </c>
+      <c r="AD92" s="2" t="inlineStr">
+        <is>
+          <t>paquete confirmado | registro definitivo OK (disponibilidad: Lima)</t>
+        </is>
+      </c>
     </row>
     <row r="93">
+      <c r="A93" s="2" t="n">
+        <v>88</v>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>TE-EMP-CM-188</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>Residencial</t>
+        </is>
+      </c>
+      <c r="I93" t="n">
+        <v>10</v>
+      </c>
+      <c r="J93" s="19" t="inlineStr">
+        <is>
+          <t>https://www.prueba.com</t>
+        </is>
+      </c>
+      <c r="K93" s="19" t="n">
+        <v>14856321</v>
+      </c>
+      <c r="L93" s="19" t="inlineStr">
+        <is>
+          <t>prueba@gmail.com</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>4 servicios: PTF + TVPR + PIF + SMQ</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>TE-PTF-CM-010</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>TE-TVPR-CM-010</t>
+        </is>
+      </c>
+      <c r="R93" s="2" t="inlineStr">
+        <is>
+          <t>TE-PIF-CM-005</t>
+        </is>
+      </c>
+      <c r="T93" s="2" t="inlineStr">
+        <is>
+          <t>TE-SMQ-CM-001</t>
+        </is>
+      </c>
       <c r="Z93" s="20">
         <f>IF(C93="","",COUNTA(N93,P93,R93,T93,V93,X93))</f>
         <v/>
       </c>
+      <c r="AA93" s="28" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr"/>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:29:33</t>
+        </is>
+      </c>
+      <c r="AD93" s="2" t="inlineStr">
+        <is>
+          <t>paquete confirmado | registro definitivo OK (disponibilidad: Lima)</t>
+        </is>
+      </c>
     </row>
     <row r="94">
+      <c r="A94" s="2" t="n">
+        <v>89</v>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>TE-EMP-CM-189</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>Residencial</t>
+        </is>
+      </c>
+      <c r="I94" t="n">
+        <v>10</v>
+      </c>
+      <c r="J94" s="19" t="inlineStr">
+        <is>
+          <t>https://www.prueba.com</t>
+        </is>
+      </c>
+      <c r="K94" s="19" t="n">
+        <v>14856321</v>
+      </c>
+      <c r="L94" s="19" t="inlineStr">
+        <is>
+          <t>prueba@gmail.com</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>4 servicios: PTF + PTV + IF + SMP</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>TE-PTF-CM-001</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>TE-PTV-CM-001</t>
+        </is>
+      </c>
+      <c r="R94" s="2" t="inlineStr">
+        <is>
+          <t>TE-IF-CM-009</t>
+        </is>
+      </c>
+      <c r="T94" s="2" t="inlineStr">
+        <is>
+          <t>TE-SMP-CM-002</t>
+        </is>
+      </c>
       <c r="Z94" s="20">
         <f>IF(C94="","",COUNTA(N94,P94,R94,T94,V94,X94))</f>
         <v/>
       </c>
+      <c r="AA94" s="28" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr"/>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:29:54</t>
+        </is>
+      </c>
+      <c r="AD94" s="2" t="inlineStr">
+        <is>
+          <t>paquete confirmado | registro definitivo OK (disponibilidad: Lima)</t>
+        </is>
+      </c>
     </row>
     <row r="95">
+      <c r="A95" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>TE-EMP-CM-190</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>Residencial</t>
+        </is>
+      </c>
+      <c r="I95" t="n">
+        <v>10</v>
+      </c>
+      <c r="J95" s="19" t="inlineStr">
+        <is>
+          <t>https://www.prueba.com</t>
+        </is>
+      </c>
+      <c r="K95" s="19" t="n">
+        <v>14856321</v>
+      </c>
+      <c r="L95" s="19" t="inlineStr">
+        <is>
+          <t>prueba@gmail.com</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>4 servicios: PTF + PTV + IF + SMC</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>TE-PTF-CM-004</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>TE-PTV-CM-004</t>
+        </is>
+      </c>
+      <c r="R95" s="2" t="inlineStr">
+        <is>
+          <t>TE-IF-CM-003</t>
+        </is>
+      </c>
+      <c r="T95" s="2" t="inlineStr">
+        <is>
+          <t>TE-SMC-CM-002</t>
+        </is>
+      </c>
       <c r="Z95" s="20">
         <f>IF(C95="","",COUNTA(N95,P95,R95,T95,V95,X95))</f>
         <v/>
       </c>
+      <c r="AA95" s="28" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr"/>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:30:15</t>
+        </is>
+      </c>
+      <c r="AD95" s="2" t="inlineStr">
+        <is>
+          <t>paquete confirmado | registro definitivo OK (disponibilidad: Lima)</t>
+        </is>
+      </c>
     </row>
     <row r="96">
+      <c r="A96" s="2" t="n">
+        <v>91</v>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>TE-EMP-CM-191</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>Residencial</t>
+        </is>
+      </c>
+      <c r="I96" t="n">
+        <v>10</v>
+      </c>
+      <c r="J96" s="19" t="inlineStr">
+        <is>
+          <t>https://www.prueba.com</t>
+        </is>
+      </c>
+      <c r="K96" s="19" t="n">
+        <v>14856321</v>
+      </c>
+      <c r="L96" s="19" t="inlineStr">
+        <is>
+          <t>prueba@gmail.com</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>4 servicios: PTF + PTV + IF + SMO</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>TE-PTF-CM-007</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>TE-PTV-CM-007</t>
+        </is>
+      </c>
+      <c r="R96" s="2" t="inlineStr">
+        <is>
+          <t>TE-IF-CM-005</t>
+        </is>
+      </c>
+      <c r="T96" s="2" t="inlineStr">
+        <is>
+          <t>TE-SMO-CM-002</t>
+        </is>
+      </c>
       <c r="Z96" s="20">
         <f>IF(C96="","",COUNTA(N96,P96,R96,T96,V96,X96))</f>
         <v/>
       </c>
+      <c r="AA96" s="28" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr"/>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:30:36</t>
+        </is>
+      </c>
+      <c r="AD96" s="2" t="inlineStr">
+        <is>
+          <t>paquete confirmado | registro definitivo OK (disponibilidad: Lima)</t>
+        </is>
+      </c>
     </row>
     <row r="97">
+      <c r="A97" s="2" t="n">
+        <v>92</v>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>TE-EMP-CM-192</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>Residencial</t>
+        </is>
+      </c>
+      <c r="I97" t="n">
+        <v>10</v>
+      </c>
+      <c r="J97" s="19" t="inlineStr">
+        <is>
+          <t>https://www.prueba.com</t>
+        </is>
+      </c>
+      <c r="K97" s="19" t="n">
+        <v>14856321</v>
+      </c>
+      <c r="L97" s="19" t="inlineStr">
+        <is>
+          <t>prueba@gmail.com</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>4 servicios: PTF + PTV + IF + SMQ</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>TE-PTF-CM-010</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>TE-PTV-CM-010</t>
+        </is>
+      </c>
+      <c r="R97" s="2" t="inlineStr">
+        <is>
+          <t>TE-IF-CM-009</t>
+        </is>
+      </c>
+      <c r="T97" s="2" t="inlineStr">
+        <is>
+          <t>TE-SMQ-CM-002</t>
+        </is>
+      </c>
       <c r="Z97" s="20">
         <f>IF(C97="","",COUNTA(N97,P97,R97,T97,V97,X97))</f>
         <v/>
       </c>
+      <c r="AA97" s="28" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr"/>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:30:58</t>
+        </is>
+      </c>
+      <c r="AD97" s="2" t="inlineStr">
+        <is>
+          <t>paquete confirmado | registro definitivo OK (disponibilidad: Lima)</t>
+        </is>
+      </c>
     </row>
     <row r="98">
+      <c r="A98" s="2" t="n">
+        <v>93</v>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>TE-EMP-CM-193</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>Residencial</t>
+        </is>
+      </c>
+      <c r="I98" t="n">
+        <v>10</v>
+      </c>
+      <c r="J98" s="19" t="inlineStr">
+        <is>
+          <t>https://www.prueba.com</t>
+        </is>
+      </c>
+      <c r="K98" s="19" t="n">
+        <v>14856321</v>
+      </c>
+      <c r="L98" s="19" t="inlineStr">
+        <is>
+          <t>prueba@gmail.com</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>4 servicios: PTF + PTV + PIF + SMP</t>
+        </is>
+      </c>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>TE-PTF-CM-001</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>TE-PTV-CM-001</t>
+        </is>
+      </c>
+      <c r="R98" s="2" t="inlineStr">
+        <is>
+          <t>TE-PIF-CM-009</t>
+        </is>
+      </c>
+      <c r="T98" s="2" t="inlineStr">
+        <is>
+          <t>TE-SMP-CM-003</t>
+        </is>
+      </c>
       <c r="Z98" s="20">
         <f>IF(C98="","",COUNTA(N98,P98,R98,T98,V98,X98))</f>
         <v/>
       </c>
+      <c r="AA98" s="28" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr"/>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:31:19</t>
+        </is>
+      </c>
+      <c r="AD98" s="2" t="inlineStr">
+        <is>
+          <t>paquete confirmado | registro definitivo OK (disponibilidad: Lima)</t>
+        </is>
+      </c>
     </row>
     <row r="99">
+      <c r="A99" s="2" t="n">
+        <v>94</v>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>TE-EMP-CM-194</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>Residencial</t>
+        </is>
+      </c>
+      <c r="I99" t="n">
+        <v>10</v>
+      </c>
+      <c r="J99" s="19" t="inlineStr">
+        <is>
+          <t>https://www.prueba.com</t>
+        </is>
+      </c>
+      <c r="K99" s="19" t="n">
+        <v>14856321</v>
+      </c>
+      <c r="L99" s="19" t="inlineStr">
+        <is>
+          <t>prueba@gmail.com</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>4 servicios: PTF + PTV + PIF + SMC</t>
+        </is>
+      </c>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>TE-PTF-CM-004</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>TE-PTV-CM-004</t>
+        </is>
+      </c>
+      <c r="R99" s="2" t="inlineStr">
+        <is>
+          <t>TE-PIF-CM-003</t>
+        </is>
+      </c>
+      <c r="T99" s="2" t="inlineStr">
+        <is>
+          <t>TE-SMC-CM-003</t>
+        </is>
+      </c>
       <c r="Z99" s="20">
         <f>IF(C99="","",COUNTA(N99,P99,R99,T99,V99,X99))</f>
         <v/>
       </c>
+      <c r="AA99" s="28" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr"/>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:59:09</t>
+        </is>
+      </c>
+      <c r="AD99" s="2" t="inlineStr">
+        <is>
+          <t>paquete confirmado | registro definitivo OK (disponibilidad: Lima)</t>
+        </is>
+      </c>
     </row>
     <row r="100">
+      <c r="A100" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>TE-EMP-CM-195</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>Residencial + Comercial</t>
+        </is>
+      </c>
+      <c r="I100" t="n">
+        <v>10</v>
+      </c>
+      <c r="J100" s="19" t="inlineStr">
+        <is>
+          <t>https://www.prueba.com</t>
+        </is>
+      </c>
+      <c r="K100" s="19" t="n">
+        <v>14856321</v>
+      </c>
+      <c r="L100" s="19" t="inlineStr">
+        <is>
+          <t>prueba@gmail.com</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>4 servicios: PTF + PTV + PIF + SMO (alcance Residencial + Comercial: SMO-005 tiene valor)</t>
+        </is>
+      </c>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>TE-PTF-CM-006</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>TE-PTV-CM-006</t>
+        </is>
+      </c>
+      <c r="R100" s="2" t="inlineStr">
+        <is>
+          <t>TE-PIF-CM-001</t>
+        </is>
+      </c>
+      <c r="T100" s="2" t="inlineStr">
+        <is>
+          <t>TE-SMO-CM-005</t>
+        </is>
+      </c>
       <c r="Z100" s="20">
         <f>IF(C100="","",COUNTA(N100,P100,R100,T100,V100,X100))</f>
         <v/>
       </c>
+      <c r="AA100" s="28" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AB100" s="2" t="inlineStr"/>
+      <c r="AC100" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:31:40</t>
+        </is>
+      </c>
+      <c r="AD100" s="2" t="inlineStr">
+        <is>
+          <t>paquete confirmado | registro definitivo OK (disponibilidad: Lima)</t>
+        </is>
+      </c>
     </row>
     <row r="101">
+      <c r="A101" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>TE-EMP-CM-196</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>Residencial</t>
+        </is>
+      </c>
+      <c r="I101" t="n">
+        <v>10</v>
+      </c>
+      <c r="J101" s="19" t="inlineStr">
+        <is>
+          <t>https://www.prueba.com</t>
+        </is>
+      </c>
+      <c r="K101" s="19" t="n">
+        <v>14856321</v>
+      </c>
+      <c r="L101" s="19" t="inlineStr">
+        <is>
+          <t>prueba@gmail.com</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>4 servicios: PTF + PTV + PIF + SMQ</t>
+        </is>
+      </c>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>TE-PTF-CM-010</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>TE-PTV-CM-010</t>
+        </is>
+      </c>
+      <c r="R101" s="2" t="inlineStr">
+        <is>
+          <t>TE-PIF-CM-009</t>
+        </is>
+      </c>
+      <c r="T101" s="2" t="inlineStr">
+        <is>
+          <t>TE-SMQ-CM-003</t>
+        </is>
+      </c>
       <c r="Z101" s="20">
         <f>IF(C101="","",COUNTA(N101,P101,R101,T101,V101,X101))</f>
         <v/>
       </c>
+      <c r="AA101" s="28" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AB101" s="2" t="inlineStr"/>
+      <c r="AC101" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:32:01</t>
+        </is>
+      </c>
+      <c r="AD101" s="2" t="inlineStr">
+        <is>
+          <t>paquete confirmado | registro definitivo OK (disponibilidad: Lima)</t>
+        </is>
+      </c>
     </row>
     <row r="102">
+      <c r="A102" s="2" t="n">
+        <v>97</v>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>TE-EMP-CM-197</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>Residencial</t>
+        </is>
+      </c>
+      <c r="I102" t="n">
+        <v>10</v>
+      </c>
+      <c r="J102" s="19" t="inlineStr">
+        <is>
+          <t>https://www.prueba.com</t>
+        </is>
+      </c>
+      <c r="K102" s="19" t="n">
+        <v>14856321</v>
+      </c>
+      <c r="L102" s="19" t="inlineStr">
+        <is>
+          <t>prueba@gmail.com</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>6 servicios: TFP + TVP + IF + SMP + AC + OS</t>
+        </is>
+      </c>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>TE-TFP-CM-001</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>TE-TVP-CM-001</t>
+        </is>
+      </c>
+      <c r="R102" s="2" t="inlineStr">
+        <is>
+          <t>TE-IF-CM-003</t>
+        </is>
+      </c>
+      <c r="T102" s="2" t="inlineStr">
+        <is>
+          <t>TE-SMP-CM-001</t>
+        </is>
+      </c>
+      <c r="V102" s="2" t="inlineStr">
+        <is>
+          <t>TE-AC-CM-001</t>
+        </is>
+      </c>
+      <c r="X102" s="2" t="inlineStr">
+        <is>
+          <t>TE-OS-CM-001</t>
+        </is>
+      </c>
       <c r="Z102" s="20">
         <f>IF(C102="","",COUNTA(N102,P102,R102,T102,V102,X102))</f>
         <v/>
       </c>
+      <c r="AA102" s="28" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AB102" s="2" t="inlineStr"/>
+      <c r="AC102" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:32:23</t>
+        </is>
+      </c>
+      <c r="AD102" s="2" t="inlineStr">
+        <is>
+          <t>paquete confirmado | registro definitivo OK (disponibilidad: Lima)</t>
+        </is>
+      </c>
     </row>
     <row r="103">
+      <c r="A103" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>TE-EMP-CM-198</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>Residencial</t>
+        </is>
+      </c>
+      <c r="I103" t="n">
+        <v>10</v>
+      </c>
+      <c r="J103" s="19" t="inlineStr">
+        <is>
+          <t>https://www.prueba.com</t>
+        </is>
+      </c>
+      <c r="K103" s="19" t="n">
+        <v>14856321</v>
+      </c>
+      <c r="L103" s="19" t="inlineStr">
+        <is>
+          <t>prueba@gmail.com</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>Solo telefonía fija: TF + TFP + OTF + PTF</t>
+        </is>
+      </c>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>TE-TF-CM-001</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>TE-TFP-CM-004</t>
+        </is>
+      </c>
+      <c r="R103" s="2" t="inlineStr">
+        <is>
+          <t>TE-OTF-CM-001</t>
+        </is>
+      </c>
+      <c r="T103" s="2" t="inlineStr">
+        <is>
+          <t>TE-PTF-CM-001</t>
+        </is>
+      </c>
       <c r="Z103" s="20">
         <f>IF(C103="","",COUNTA(N103,P103,R103,T103,V103,X103))</f>
         <v/>
       </c>
+      <c r="AA103" s="28" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AB103" s="2" t="inlineStr"/>
+      <c r="AC103" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:32:44</t>
+        </is>
+      </c>
+      <c r="AD103" s="2" t="inlineStr">
+        <is>
+          <t>paquete confirmado | registro definitivo OK (disponibilidad: Lima)</t>
+        </is>
+      </c>
     </row>
     <row r="104">
+      <c r="A104" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>TE-EMP-CM-199</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>Residencial</t>
+        </is>
+      </c>
+      <c r="I104" t="n">
+        <v>10</v>
+      </c>
+      <c r="J104" s="19" t="inlineStr">
+        <is>
+          <t>https://www.prueba.com</t>
+        </is>
+      </c>
+      <c r="K104" s="19" t="n">
+        <v>14856321</v>
+      </c>
+      <c r="L104" s="19" t="inlineStr">
+        <is>
+          <t>prueba@gmail.com</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>Solo internet fijo: IF + PIF (PIF vale 0: no cumple la regla de precios)</t>
+        </is>
+      </c>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>TE-IF-CM-005</t>
+        </is>
+      </c>
+      <c r="P104" s="2" t="inlineStr">
+        <is>
+          <t>TE-PIF-CM-003</t>
+        </is>
+      </c>
       <c r="Z104" s="20">
         <f>IF(C104="","",COUNTA(N104,P104,R104,T104,V104,X104))</f>
         <v/>
       </c>
+      <c r="AA104" s="23" t="inlineStr">
+        <is>
+          <t>Omitida</t>
+        </is>
+      </c>
+      <c r="AB104" s="2" t="inlineStr"/>
+      <c r="AC104" s="2" t="inlineStr"/>
+      <c r="AD104" s="2" t="inlineStr"/>
     </row>
     <row r="105">
+      <c r="A105" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>TE-EMP-CM-200</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>Residencial</t>
+        </is>
+      </c>
+      <c r="I105" t="n">
+        <v>10</v>
+      </c>
+      <c r="J105" s="19" t="inlineStr">
+        <is>
+          <t>https://www.prueba.com</t>
+        </is>
+      </c>
+      <c r="K105" s="19" t="n">
+        <v>14856321</v>
+      </c>
+      <c r="L105" s="19" t="inlineStr">
+        <is>
+          <t>prueba@gmail.com</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr">
+        <is>
+          <t>Solo TV de paga: TVP + TVPR + PTV</t>
+        </is>
+      </c>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>TE-TVP-CM-004</t>
+        </is>
+      </c>
+      <c r="P105" s="2" t="inlineStr">
+        <is>
+          <t>TE-TVPR-CM-001</t>
+        </is>
+      </c>
+      <c r="R105" s="2" t="inlineStr">
+        <is>
+          <t>TE-PTV-CM-001</t>
+        </is>
+      </c>
       <c r="Z105" s="20">
         <f>IF(C105="","",COUNTA(N105,P105,R105,T105,V105,X105))</f>
         <v/>
       </c>
+      <c r="AA105" s="28" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AB105" s="2" t="inlineStr"/>
+      <c r="AC105" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:33:05</t>
+        </is>
+      </c>
+      <c r="AD105" s="2" t="inlineStr">
+        <is>
+          <t>paquete confirmado | registro definitivo OK (disponibilidad: Lima)</t>
+        </is>
+      </c>
     </row>
     <row r="106">
+      <c r="A106" s="2" t="n">
+        <v>101</v>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>TE-EMP-CM-201</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>Residencial</t>
+        </is>
+      </c>
+      <c r="J106" s="19" t="inlineStr">
+        <is>
+          <t>https://www.prueba.com</t>
+        </is>
+      </c>
+      <c r="K106" s="19" t="n">
+        <v>14856321</v>
+      </c>
+      <c r="L106" s="19" t="inlineStr">
+        <is>
+          <t>prueba@gmail.com</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="inlineStr">
+        <is>
+          <t>Solo móvil: SMP + SMC + SMO + SMQ</t>
+        </is>
+      </c>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>TE-SMP-CM-002</t>
+        </is>
+      </c>
+      <c r="P106" s="2" t="inlineStr">
+        <is>
+          <t>TE-SMC-CM-001</t>
+        </is>
+      </c>
+      <c r="R106" s="2" t="inlineStr">
+        <is>
+          <t>TE-SMO-CM-001</t>
+        </is>
+      </c>
+      <c r="T106" s="2" t="inlineStr">
+        <is>
+          <t>TE-SMQ-CM-001</t>
+        </is>
+      </c>
       <c r="Z106" s="20">
         <f>IF(C106="","",COUNTA(N106,P106,R106,T106,V106,X106))</f>
         <v/>
+      </c>
+      <c r="AA106" s="28" t="inlineStr">
+        <is>
+          <t>Registro definitivo</t>
+        </is>
+      </c>
+      <c r="AB106" s="2" t="inlineStr"/>
+      <c r="AC106" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:33:19</t>
+        </is>
+      </c>
+      <c r="AD106" s="2" t="inlineStr">
+        <is>
+          <t>paquete confirmado | registro definitivo OK</t>
+        </is>
       </c>
     </row>
     <row r="107">
@@ -7367,16 +15636,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:AD10"/>
-  <dataValidations count="3">
-    <dataValidation sqref="B6:B1005" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Listas!$A$1:$A$2</formula1>
-    </dataValidation>
-    <dataValidation sqref="D6:D1005" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Listas!$A$1:$A$2</formula1>
+  <autoFilter ref="A5:AD106"/>
+  <dataValidations count="2">
+    <dataValidation sqref="B6:B1005 D6:D1005" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>Listas!$A$1:$A$2</formula1>
     </dataValidation>
     <dataValidation sqref="F6:F1005" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Listas!$B$1:$B$3</formula1>
+      <formula1>Listas!$B$1:$B$3</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7390,7 +15656,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
